--- a/data_extactor/batch/701_750.xlsx
+++ b/data_extactor/batch/701_750.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700B545B-CF5D-48F0-9B48-CED0EA9AFD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1603 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="530">
+  <si>
+    <t>45-2091.00</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators</t>
+  </si>
+  <si>
+    <t>Baler Operator | Cutter Operator | Equipment Operator | Farm Equipment Operator | Hay Baler | Loader Operator | Packing Tractor Machine Operator | Rake Operator | Sprayer | Windrower Operator</t>
+  </si>
+  <si>
+    <t>Farm Management Software Hay and Crop Manager | Martens Farms Farm Site Mate | Martens Farms Farm Trac | Microsoft Access | Microsoft Excel | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Active Listening</t>
+  </si>
+  <si>
+    <t>English Language</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Near Vision | Depth Perception | Far Vision | Problem Sensitivity | Response Orientation | Rate Control | Reaction Time | Oral Comprehension | Arm-Hand Steadiness | Manual Dexterity | Oral Expression | Hearing Sensitivity | Trunk Strength | Static Strength | Speech Clarity | Speech Recognition | Extent Flexibility | Finger Dexterity | Information Ordering | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Very Hot or Cold Temperatures | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Contact With Others | In an Open Vehicle or Operating Equipment | Exposed to Contaminants | Pace Determined by Speed of Equipment</t>
+  </si>
+  <si>
+    <t>Conveyor Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Excavating and Loading Machine and Dragline Operators, Surface Mining | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Operating Engineers and Other Construction Equipment Operators | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Paving, Surfacing, and Tamping Equipment Operators | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Drive and control equipment to support agricultural activities such as tilling soil; planting, cultivating, and harvesting crops; feeding and herding livestock; or removing animal waste. May perform tasks such as crop baling or hay bucking. May operate stationary equipment to perform post-harvest tasks such as husking, shelling, threshing, and ginning.</t>
+  </si>
+  <si>
+    <t>Adjust, repair, and service farm machinery and notify supervisors when machinery malfunctions. | Attach farm implements such as plows, discs, sprayers, or harvesters to tractors, using bolts and hand tools. | Direct and monitor the activities of work crews engaged in planting, weeding, or harvesting activities. | Drive trucks to haul crops, supplies, tools, or farm workers. | Guide products on conveyors to regulate flow through machines, and to discard diseased or rotten products. | Irrigate soil, using portable pipes or ditch systems, and maintain ditches or pipes and pumps. | Load and unload crops or containers of materials, manually or using conveyors, handtrucks, forklifts, or transfer augers. | Load hoppers, containers, or conveyors to feed machines with products, using forklifts, transfer augers, suction gates, shovels, or pitchforks. | Manipulate controls to set, activate, and adjust mechanisms on machinery. | Mix specified materials or chemicals, and dump solutions, powders, or seeds into planter or sprayer machinery. | Observe and listen to machinery operation to detect equipment malfunctions. | Operate or tend equipment used in agricultural production, such as tractors, combines, and irrigation equipment. | Operate towed machines such as seed drills or manure spreaders to plant, fertilize, dust, and spray crops. | Position boxes or attach bags at discharge ends of machinery to catch products, removing and closing full containers. | Spray fertilizer or pesticide solutions to control insects, fungus and weed growth, and diseases, using hand sprayers. | Walk beside or ride on planting machines while inserting plants in planter mechanisms at specified intervals. | Weigh crop-filled containers, and record weights and other identifying information.</t>
+  </si>
+  <si>
+    <t>45-2092.00</t>
+  </si>
+  <si>
+    <t>Farmworkers and Laborers, Crop, Nursery, and Greenhouse</t>
+  </si>
+  <si>
+    <t>Farm Laborer | Farmer | Field Irrigation Worker | Gardener | Greenhouse Worker | Grower | Harvester | Nursery Worker | Orchard Worker | Picker</t>
+  </si>
+  <si>
+    <t>BCL Landview Systems WinCrop | Farm Works Software Trac | Global positioning system GPS software | IBM Lotus Notes | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking</t>
+  </si>
+  <si>
+    <t>Food Production | Biology | English Language | Mechanical | Public Safety and Security | Chemistry</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Arm-Hand Steadiness | Control Precision | Extent Flexibility | Manual Dexterity | Multilimb Coordination | Finger Dexterity | Static Strength | Dynamic Strength | Rate Control | Near Vision | Stamina | Explosive Strength | Oral Expression | Reaction Time | Oral Comprehension | Far Vision | Gross Body Coordination | Speech Clarity | Speech Recognition | Gross Body Equilibrium | Deductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Spend Time Making Repetitive Motions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Time Pressure | Spend Time Standing | Spend Time Bending or Twisting Your Body | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Agricultural Technicians | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Fallers | Farmers, Ranchers, and Other Agricultural Managers | Farmworkers, Farm, Ranch, and Aquacultural Animals | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Food Batchmakers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Forest and Conservation Workers | Graders and Sorters, Agricultural Products | Laborers and Freight, Stock, and Material Movers, Hand | Landscaping and Groundskeeping Workers | Machine Feeders and Offbearers | Meat, Poultry, and Fish Cutters and Trimmers | Packers and Packagers, Hand | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Soil and Plant Scientists | Tree Trimmers and Pruners</t>
+  </si>
+  <si>
+    <t>Manually plant, cultivate, and harvest vegetables, fruits, nuts, horticultural specialties, and field crops. Use hand tools, such as shovels, trowels, hoes, tampers, pruning hooks, shears, and knives. Duties may include tilling soil and applying fertilizers; transplanting, weeding, thinning, or pruning crops; applying pesticides; or cleaning, grading, sorting, packing, and loading harvested products. May construct trellises, repair fences and farm buildings, or participate in irrigation activities.</t>
+  </si>
+  <si>
+    <t>Clean work areas, and maintain grounds and landscaping. | Dig, cut, and transplant seedlings, cuttings, trees, and shrubs. | Dig, rake, and screen soil, filling cold frames and hot beds in preparation for planting. | Direct and monitor the work of casual and seasonal help during planting and harvesting. | Feel plants' leaves and note their coloring to detect the presence of insects or disease. | Harvest fruits and vegetables by hand. | Harvest plants, and transplant or pot and label them. | Haul and spread topsoil, fertilizer, peat moss, and other materials to condition soil, using wheelbarrows or carts and shovels. | Identify plants, pests, and weeds to determine the selection and application of pesticides and fertilizers. | Inform farmers or farm managers of crop progress. | Inspect plants and bud ties to assess quality. | Load agricultural products into trucks, and drive trucks to market or storage facilities. | Maintain and repair irrigation and climate control systems. | Maintain inventory, ordering materials as required. | Move containerized shrubs, plants, and trees, using wheelbarrows or tractors. | Operate tractors, tractor-drawn machinery, and self-propelled machinery to plow, harrow and fertilize soil, or to plant, cultivate, spray and harvest crops. | Participate in the inspection, grading, sorting, storage, and post-harvest treatment of crops. | Plant, spray, weed, fertilize, water, and prune plants, shrubs, and trees, using gardening tools. | Provide information and advice to the public regarding the selection, purchase, and care of products. | Record information about crops, such as pesticide use, yields, or costs. | Record information about plants and plant growth. | Regulate greenhouse conditions, and indoor and outdoor irrigation systems. | Repair and maintain farm vehicles, implements, and mechanical equipment. | Repair farm buildings, fences, and other structures. | Sell and deliver plants and flowers to customers. | Set up and operate irrigation equipment. | Tie and bunch flowers, plants, shrubs, and trees, wrap their roots, and pack them into boxes to fill orders.</t>
+  </si>
+  <si>
+    <t>45-2093.00</t>
+  </si>
+  <si>
+    <t>Farmworkers, Farm, Ranch, and Aquacultural Animals</t>
+  </si>
+  <si>
+    <t>Cowboy | Farm Hand | Farrowing Worker | Herdsman | Livestock Handler | Milking Worker | Ranch Hand | Rancher | Vaccinator | Wrangler</t>
+  </si>
+  <si>
+    <t>BCL Landview Systems WinCrop | Farm Works Software Trac | Lancaster DHIA PCDART | Microsoft Excel | Microsoft Office software | Microsoft Word | Valley Agricultural Software DairyCOMP 305 | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Biology | Administration and Management | English Language | Mechanical | Food Production | Mathematics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Control Precision | Arm-Hand Steadiness | Deductive Reasoning | Oral Comprehension | Near Vision | Trunk Strength | Information Ordering | Inductive Reasoning | Speech Clarity | Far Vision | Static Strength | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Speech Recognition | Selective Attention | Flexibility of Closure | Category Flexibility | Oral Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Outdoors, Exposed to All Weather Conditions | Contact With Others | Telephone Conversations | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Walking or Running | Exposed to Very Hot or Cold Temperatures | Outdoors, Under Cover | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Frequency of Decision Making | Physical Proximity | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Agricultural Technicians | Animal Breeders | Animal Caretakers | Animal Scientists | Buyers and Purchasing Agents, Farm Products | Farmers, Ranchers, and Other Agricultural Managers | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Fishing and Hunting Workers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Helpers--Production Workers | Laborers and Freight, Stock, and Material Movers, Hand | Machine Feeders and Offbearers | Meat, Poultry, and Fish Cutters and Trimmers | Packers and Packagers, Hand | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Slaughterers and Meat Packers</t>
+  </si>
+  <si>
+    <t>Attend to live farm, ranch, open range or aquacultural animals that may include cattle, sheep, swine, goats, horses and other equines, poultry, rabbits, finfish, shellfish, and bees. Attend to animals produced for animal products, such as meat, fur, skins, feathers, eggs, milk, and honey. Duties may include feeding, watering, herding, grazing, milking, castrating, branding, de-beaking, weighing, catching, and loading animals. May maintain records on animals; examine animals to detect diseases and injuries; assist in birth deliveries; and administer medications, vaccinations, or insecticides as appropriate. May clean and maintain animal housing areas. Includes workers who shear wool from sheep and collect eggs in hatcheries.</t>
+  </si>
+  <si>
+    <t>Clean stalls, pens, and equipment, using disinfectant solutions, brushes, shovels, water hoses, or pumps. | Drive trucks, tractors, and other equipment to distribute feed to animals. | Examine animals to detect illness, injury, or disease, and to check physical characteristics, such as rate of weight gain. | Feed and water livestock and monitor food and water supplies. | Groom, clip, trim, or castrate animals, dock ears and tails, or shear coats to collect hair. | Herd livestock to pastures for grazing or to scales, trucks, or other enclosures. | Inspect, maintain, and repair equipment, machinery, buildings, pens, yards, and fences. | Maintain growth, feeding, production, and cost records. | Mark livestock to identify ownership and grade, using brands, tags, paint, or tattoos. | Mix feed, additives, and medicines in prescribed portions. | Move equipment, poultry, or livestock from one location to another, manually or using trucks or carts. | Order food for animals, and arrange for its delivery. | Patrol grazing lands on horseback or using all-terrain vehicles. | Perform duties related to livestock reproduction, such as breeding animals within appropriate timeframes, performing artificial inseminations, and helping with animal births. | Protect herds from predators, using trained dogs. | Provide medical treatment, such as administering medications and vaccinations, or arrange for veterinarians to provide more extensive treatment. | Segregate animals according to weight, age, color, and physical condition. | Shift animals between grazing areas to ensure that they have sufficient access to food. | Spray livestock with disinfectants and insecticides, or dip or bathe animals.</t>
+  </si>
+  <si>
+    <t>45-2099.00</t>
+  </si>
+  <si>
+    <t>Agricultural Workers, All Other</t>
+  </si>
+  <si>
+    <t>Agricultural Laborer | Agricultural Worker | Apiary Worker | Farm Hand | Farm Worker | Field Worker | Irrigation Worker | Livestock Worker | Orchard Worker | Vineyard Worker</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Food Production | Mechanical | Biology | English Language | Public Safety and Security | Chemistry | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | In an Open Vehicle or Operating Equipment | Exposed to Very Hot or Cold Temperatures | Spend Time Standing | Spend Time Walking or Running | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Bending or Twisting Your Body | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Physical Proximity | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Farmworkers, Farm, Ranch, and Aquacultural Animals | Agricultural Equipment Operators | Graders and Sorters, Agricultural Products | Animal Breeders | Agricultural Inspectors | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Fishing and Hunting Workers | Forest and Conservation Workers | Landscaping and Groundskeeping Workers | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Farmers, Ranchers, and Other Agricultural Managers | Agricultural Technicians | Precision Agriculture Technicians | Animal Caretakers | Food Batchmakers | Packers and Packagers, Hand | Laborers and Freight, Stock, and Material Movers, Hand | Farm Equipment Mechanics and Service Technicians | Farm Labor Contractors</t>
+  </si>
+  <si>
+    <t>All agricultural workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform agricultural work in roles not classified separately. | Plant, cultivate, irrigate, and harvest crops according to established schedules. | Operate and adjust tractors, implements, and hand tools used in production. | Apply fertilizers, pesticides, and soil amendments following label directions. | Inspect crops and livestock for signs of disease, pests, or poor condition. | Feed, water, and monitor the health and behavior of animals. | Repair and maintain fences, irrigation lines, buildings, and equipment. | Sort, grade, clean, and pack products for storage or shipment. | Load and unload produce, feed, supplies, and equipment. | Record production data, applications, yields, and animal health information. | Follow safety procedures for machinery, chemicals, and livestock handling. | Clean and sanitize work areas, containers, and equipment. | Assist with breeding, birthing, and animal husbandry activities. | Monitor weather, soil, and moisture conditions affecting operations.</t>
+  </si>
+  <si>
+    <t>45-3031.00</t>
+  </si>
+  <si>
+    <t>Fishing and Hunting Workers</t>
+  </si>
+  <si>
+    <t>Commercial Fisherman | Commercial Fishing Vessel Operator | Deckhand | Fisherman | Fur Trapper | Hunter | Lobster Fisherman | Nuisance Trapper | Trapper | Wildlife Control Operator</t>
+  </si>
+  <si>
+    <t>Catchlog Trading Catchlog | DeerDays | Inventory management systems | MaxSea TIMEZERO | MaxSea Time Zero Navigator NOAA | Microsoft Excel | Microsoft Office software | OLRAC Electronic Logbook Software Solution | P-Sea WindPlot | Signet Nobeltec Catch | Strat-Tech Deer Hunting Expert | Trimble MyTopo Terrain Navigator Pro | Winchester Ammunition Ballistics Calculator</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Geography | Mechanical | Law and Government | Customer and Personal Service | Biology | English Language | Sales and Marketing | Education and Training</t>
+  </si>
+  <si>
+    <t>Spatial Orientation | Far Vision | Static Strength | Flexibility of Closure | Near Vision | Trunk Strength | Arm-Hand Steadiness | Inductive Reasoning | Problem Sensitivity | Manual Dexterity | Control Precision | Multilimb Coordination | Depth Perception | Oral Comprehension | Oral Expression | Deductive Reasoning | Extent Flexibility | Dynamic Strength | Reaction Time | Speech Clarity | Hearing Sensitivity | Visual Color Discrimination | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Contact With Others | Exposed to Extremely Bright or Inadequate Lighting Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Level of Competition | Exposed to Very Hot or Cold Temperatures | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Determine Tasks, Priorities and Goals | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Physical Proximity | Indoors, Not Environmentally Controlled | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Captains, Mates, and Pilots of Water Vessels | Commercial Divers | Crane and Tower Operators | Dredge Operators | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Farmworkers, Farm, Ranch, and Aquacultural Animals | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Fish and Game Wardens | Forest and Conservation Workers | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Machine Feeders and Offbearers | Meat, Poultry, and Fish Cutters and Trimmers | Motorboat Operators | Riggers | Sailors and Marine Oilers | Ship Engineers</t>
+  </si>
+  <si>
+    <t>Hunt, trap, catch, or gather wild animals or aquatic animals and plants. May use nets, traps, or other equipment. May haul catch onto ship or other vessel.</t>
+  </si>
+  <si>
+    <t>Attach nets, slings, hooks, blades, or lifting devices to cables, booms, hoists, or dredges. | Compute positions and plot courses on charts to navigate vessels, using instruments such as compasses, sextants, and charts. | Connect accessories such as floats, weights, flags, lights, or markers to nets, lines, or traps. | Direct fishing or hunting operations, and supervise crew members. | Harvest marine life for human or animal consumption, using diving or dredging equipment, traps, barges, rods, reels, or tackle. | Interpret weather and vessel conditions to determine appropriate responses. | Kill or stun trapped quarry, using clubs, poisons, guns, or drowning methods. | Load and unload vessel equipment and supplies, by hand or using hoisting equipment. | Locate fish, using fish-finding equipment. | Maintain and repair trapping equipment. | Maintain engines, fishing gear, and other on-board equipment and perform minor repairs. | Obtain permission from landowners to hunt or trap on their land. | Obtain required approvals for using poisons or traps, and notify persons in areas where traps and poison are set. | Oversee the purchase of supplies, gear, and equipment. | Participate in animal damage control, wildlife management, disease control, and research activities. | Patrol trap lines or nets to inspect settings, remove catch, and reset or relocate traps. | Put fishing equipment into the water and anchor or tow equipment, according to the fishing method used. | Release quarry from traps or nets and transfer to cages. | Remove catches from fishing equipment and measure them to ensure compliance with legal size. | Scrape fat, blubber, or flesh from skin sides of pelts with knives or hand scrapers. | Select, bait, and set traps, and lay poison along trails, according to species, size, habits, and environs of birds or animals and reasons for trapping them. | Skin quarry, using knives, and stretch pelts on frames to be cured. | Sort, pack, and store catch in holds with salt and ice. | Steer vessels and operate navigational instruments. | Teach or guide individuals or groups unfamiliar with specific hunting methods or types of prey. | Track animals by checking for signs such as droppings or destruction of vegetation. | Transport fish to processing plants or to buyers. | Travel on foot, by vehicle, or by equipment such as boats, snowmobiles, helicopters, snowshoes, or skis to reach hunting areas. | Wash decks, conveyors, knives, and other equipment, using brushes, detergents, and water.</t>
+  </si>
+  <si>
+    <t>45-4011.00</t>
+  </si>
+  <si>
+    <t>Forest and Conservation Workers</t>
+  </si>
+  <si>
+    <t>Christmas Tree Farmer | Conservation Officer | Field Laborer | Forest Ranger | Forest Resource Specialist | Forestry Support Specialist | Park Maintainer | Reforestation Worker | Tree Farmer | Tree Planter</t>
+  </si>
+  <si>
+    <t>Database software | ESRI ArcGIS software | Geographic information system GIS software | Geographic information system GIS systems | IBM Lotus 1-2-3 | IBM Lotus Notes | Leica Geosystems ERDAS IMAGINE | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Learning | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | English Language | Customer and Personal Service | Administration and Management | Geography | Biology</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Oral Expression | Static Strength | Deductive Reasoning | Far Vision | Near Vision | Stamina | Trunk Strength | Dynamic Strength | Multilimb Coordination | Flexibility of Closure | Speech Clarity | Speech Recognition | Depth Perception | Control Precision | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Visualization | Perceptual Speed | Category Flexibility | Information Ordering | Inductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Work With or Contribute to a Work Group or Team | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Deal With External Customers or the Public in General | Health and Safety of Other Workers | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Agricultural Technicians | Conservation Scientists | Environmental Restoration Planners | Environmental Scientists and Specialists, Including Health | Fallers | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Firefighters | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | Fish and Game Wardens | Forest Fire Inspectors and Prevention Specialists | Forest and Conservation Technicians | Foresters | Landscaping and Groundskeeping Workers | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Range Managers | Soil and Plant Scientists | Tree Trimmers and Pruners | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Under supervision, perform manual labor necessary to develop, maintain, or protect areas such as forests, forested areas, woodlands, wetlands, and rangelands through such activities as raising and transporting seedlings; combating insects, pests, and diseases harmful to plant life; and building structures to control water, erosion, and leaching of soil. Includes forester aides, seedling pullers, tree planters, and gatherers of nontimber forestry products such as pine straw.</t>
+  </si>
+  <si>
+    <t>Check equipment to ensure that it is operating properly. | Confer with other workers to discuss issues, such as safety, cutting heights, or work needs. | Erect signs or fences, using posthole diggers, shovels, or other hand tools. | Explain or enforce regulations regarding camping, vehicle use, fires, use of buildings, or sanitation. | Fight forest fires or perform prescribed burning tasks under the direction of fire suppression officers or forestry technicians. | Identify diseased or undesirable trees and remove them, using power saws or hand saws. | Maintain campsites or recreational areas, replenishing firewood or other supplies and cleaning kitchens or restrooms. | Maintain tallies of trees examined and counted during tree marking or measuring efforts. | Operate skidders, bulldozers, or other prime movers to pull a variety of scarification or site preparation equipment over areas to be regenerated. | Perform fire protection or suppression duties, such as constructing fire breaks or disposing of brush. | Provide assistance to forest survey crews by clearing site-lines, holding measuring tools, or setting stakes. | Prune or shear tree tops or limbs to control growth, increase density, or improve shape. | Select or cut trees according to markings or sizes, types, or grades. | Select tree seedlings, prepare the ground, or plant the trees in reforestation areas, using manual planting tools. | Sort tree seedlings, discarding substandard seedlings, according to standard charts or verbal instructions. | Spray or inject vegetation with insecticides to kill insects or to protect against disease or with herbicides to reduce competing vegetation. | Thin or space trees, using power thinning saws.</t>
+  </si>
+  <si>
+    <t>45-4021.00</t>
+  </si>
+  <si>
+    <t>Fallers</t>
+  </si>
+  <si>
+    <t>Cutter Operator | Logger | Sawyer | Timber Cutter | Timber Faller | Tree Faller | Tree Feller | Tree Topper</t>
+  </si>
+  <si>
+    <t>Assisi Compiler | Assisi Software Assisi Inventory | Assisi Software Assisi Manager | Assisi Software Assisi Resource | BCS Woodlands Software The Logger Tracker | BCS Woodlands Software Woodlands Tracker | ESRI ArcView | Geographic information system GIS systems | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Biology | English Language | Mathematics | Production and Processing</t>
+  </si>
+  <si>
+    <t>Reaction Time | Multilimb Coordination | Control Precision | Static Strength | Speed of Limb Movement | Manual Dexterity | Arm-Hand Steadiness | Auditory Attention | Depth Perception | Gross Body Coordination | Stamina | Trunk Strength | Near Vision | Far Vision | Visual Color Discrimination | Hearing Sensitivity | Extent Flexibility | Flexibility of Closure | Information Ordering | Problem Sensitivity | Rate Control | Response Orientation | Visualization | Gross Body Equilibrium | Dynamic Strength | Perceptual Speed | Category Flexibility | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Standing | Exposed to Contaminants | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Exposed to Whole Body Vibration | Spend Time Bending or Twisting Your Body | Importance of Being Exact or Accurate | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Carpenters | Earth Drillers, Except Oil and Gas | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Forest and Conservation Technicians | Forest and Conservation Workers | Foresters | Helpers--Extraction Workers | Hoist and Winch Operators | Landscaping and Groundskeeping Workers | Log Graders and Scalers | Logging Equipment Operators | Operating Engineers and Other Construction Equipment Operators | Rail-Track Laying and Maintenance Equipment Operators | Riggers | Rock Splitters, Quarry | Sawing Machine Setters, Operators, and Tenders, Wood | Tree Trimmers and Pruners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Use axes or chainsaws to fell trees using knowledge of tree characteristics and cutting techniques to control direction of fall and minimize tree damage.</t>
+  </si>
+  <si>
+    <t>Appraise trees for certain characteristics, such as twist, rot, and heavy limb growth, and gauge amount and direction of lean, to determine how to control the direction of a tree's fall with the least damage. | Assess logs after cutting to ensure that the quality and length are correct. | Clear brush from work areas and escape routes, and cut saplings and other trees from direction of falls, using axes, chainsaws, or bulldozers. | Control the direction of a tree's fall by scoring cutting lines with axes, sawing undercuts along scored lines with chainsaws, knocking slabs from cuts with single-bit axes, and driving wedges. | Determine position, direction, and depth of cuts to be made, and placement of wedges or jacks. | Insert jacks or drive wedges behind saws to prevent binding of saws and to start trees falling. | Load logs or wood onto trucks, trailers, or railroad cars, by hand or using loaders or winches. | Maintain and repair chainsaws and other equipment, cleaning, oiling, and greasing equipment, and sharpening equipment properly. | Mark logs for identification. | Measure felled trees and cut them into specified log lengths, using chain saws and axes. | Place supporting limbs or poles under felled trees to avoid splitting undersides, and to prevent logs from rolling. | Saw back-cuts, leaving sufficient sound wood to control direction of fall. | Secure steel cables or chains to logs for dragging by tractors or for pulling by cable yarding systems. | Select trees to be cut down, assessing factors such as site, terrain, and weather conditions before beginning work. | Stop saw engines, pull cutting bars from cuts, and run to safety as tree falls. | Tag unsafe trees with high-visibility ribbons. | Trim off the tops and limbs of trees, using chainsaws, delimbers, or axes. | Work as a member of a team, rotating between chain saw operation and skidder operation.</t>
+  </si>
+  <si>
+    <t>45-4022.00</t>
+  </si>
+  <si>
+    <t>Logging Equipment Operators</t>
+  </si>
+  <si>
+    <t>Delimber Operator | Feller Buncher Operator | Harvester Operator | Loader Operator | Log Processor Operator | Logging Equipment Operator | Logging Shovel Operator | Skidder Driver | Skidder Operator | Yarder Operator</t>
+  </si>
+  <si>
+    <t>BCS Woodlands Systems The Logger Tracker | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | SAP software | TradeTec TallyWorks Logs | TradeTec TallyWorks TimeTracker</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Production and Processing</t>
+  </si>
+  <si>
+    <t>Control Precision | Reaction Time | Multilimb Coordination | Arm-Hand Steadiness | Depth Perception | Response Orientation | Problem Sensitivity | Far Vision | Rate Control | Near Vision | Manual Dexterity | Visualization | Perceptual Speed | Visual Color Discrimination | Trunk Strength | Finger Dexterity | Selective Attention | Spatial Orientation | Category Flexibility | Information Ordering | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Enclosed Vehicle or Operate Enclosed Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Spend Time Sitting | Work With or Contribute to a Work Group or Team | Outdoors, Exposed to All Weather Conditions | Contact With Others | Spend Time Making Repetitive Motions | Consequence of Error | Telephone Conversations | Freedom to Make Decisions | Exposed to Whole Body Vibration | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Exposed to Hazardous Equipment | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Bus and Truck Mechanics and Diesel Engine Specialists | Continuous Mining Machine Operators | Conveyor Operators and Tenders | Crane and Tower Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Fallers | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Log Graders and Scalers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Roustabouts, Oil and Gas | Sawing Machine Setters, Operators, and Tenders, Wood | Tank Car, Truck, and Ship Loaders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Drive logging tractor or wheeled vehicle equipped with one or more accessories, such as bulldozer blade, frontal shear, grapple, logging arch, cable winches, hoisting rack, or crane boom, to fell tree; to skid, load, unload, or stack logs; or to pull stumps or clear brush. Includes operating stand-alone logging machines, such as log chippers.</t>
+  </si>
+  <si>
+    <t>Calculate total board feet, cordage, or other wood measurement units, using conversion tables. | Control hydraulic tractors equipped with tree clamps and booms to lift, swing, and bunch sheared trees. | Drive and maneuver tractors and tree harvesters to shear the tops off of trees, cut and limb the trees, and cut the logs into desired lengths. | Drive crawler or wheeled tractors to drag or transport logs from felling sites to log landing areas for processing and loading. | Drive straight or articulated tractors equipped with accessories such as bulldozer blades, grapples, logging arches, cable winches, and crane booms to skid, load, unload, or stack logs, pull stumps, or clear brush. | Drive tractors for building or repairing logging and skid roads. | Fill out required job or shift report forms. | Grade logs according to characteristics such as knot size and straightness, and according to established industry or company standards. | Inspect equipment for safety prior to use, and perform necessary basic maintenance tasks.</t>
+  </si>
+  <si>
+    <t>45-4023.00</t>
+  </si>
+  <si>
+    <t>Log Graders and Scalers</t>
+  </si>
+  <si>
+    <t>Log Buyer | Log Check Scaler | Log Grader | Log Scaler | Lumber Grader | Scaler | Timber Buyer</t>
+  </si>
+  <si>
+    <t>AS/400 Database | Atterbury Consultants SuperACE/FLIPS | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Active Learning | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics | Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Oral Expression | Oral Comprehension | Deductive Reasoning | Inductive Reasoning | Category Flexibility | Written Expression | Far Vision | Perceptual Speed | Flexibility of Closure | Speech Clarity | Speech Recognition | Visual Color Discrimination | Control Precision | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Number Facility | Mathematical Reasoning | Information Ordering | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Exposed to Very Hot or Cold Temperatures | Time Pressure | Contact With Others | Determine Tasks, Priorities and Goals | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Telephone Conversations | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Fallers | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Graders and Sorters, Agricultural Products | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Inspectors, Testers, Sorters, Samplers, and Weighers | Laborers and Freight, Stock, and Material Movers, Hand | Logging Equipment Operators | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Packers and Packagers, Hand | Production, Planning, and Expediting Clerks | Shipping, Receiving, and Inventory Clerks | Tool Grinders, Filers, and Sharpeners | Weighers, Measurers, Checkers, and Samplers, Recordkeeping | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Grade logs or estimate the marketable content or value of logs or pulpwood in sorting yards, millpond, log deck, or similar locations. Inspect logs for defects or measure logs to determine volume.</t>
+  </si>
+  <si>
+    <t>Arrange for hauling of logs to appropriate mill sites. | Communicate with coworkers by signals to direct log movement. | Drive to sawmills, wharfs, or skids to inspect logs or pulpwood. | Evaluate log characteristics and determine grades, using established criteria. | Identify logs of substandard or special grade so that they can be returned to shippers, regraded, recut, or transferred for other processing. | Jab logs with metal ends of scale sticks, and inspect logs to ascertain characteristics or defects such as water damage, splits, knots, broken ends, rotten areas, twists, and curves. | Measure felled logs or loads of pulpwood to calculate volume, weight, dimensions, and marketable value, using measuring devices and conversion tables. | Measure log lengths and mark boles for bucking into logs, according to specifications. | Paint identification marks of specified colors on logs to identify grades or species, using spray cans, or call out grades to log markers. | Record data about individual trees or load volumes into tally books or hand-held collection terminals. | Saw felled trees into lengths. | Weigh log trucks before and after unloading, and record load weights and supplier identities.</t>
+  </si>
+  <si>
+    <t>45-4029.00</t>
+  </si>
+  <si>
+    <t>Logging Workers, All Other</t>
+  </si>
+  <si>
+    <t>Choke Setter | Logger | Logging Worker | Log Handler | Rigging Slinger | Timber Cutter | Timber Worker | Yarder Operator | Log Loader Operator | Forest Products Worker</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | English Language | Production and Processing | Biology | Transportation | Mathematics</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Health and Safety of Other Workers | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Consequence of Error | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Whole Body Vibration | In an Open Vehicle or Operating Equipment</t>
+  </si>
+  <si>
+    <t>Fallers | Logging Equipment Operators | Log Graders and Scalers | Forest and Conservation Workers | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Forest and Conservation Technicians | Tree Trimmers and Pruners | Foresters | Operating Engineers and Other Construction Equipment Operators | Heavy and Tractor-Trailer Truck Drivers | Crane and Tower Operators | Hoist and Winch Operators | Construction Laborers | Riggers | Mobile Heavy Equipment Mechanics, Except Engines | Sawing Machine Setters, Operators, and Tenders, Wood | Laborers and Freight, Stock, and Material Movers, Hand | Conservation Scientists | Agricultural Equipment Operators | Industrial Truck and Tractor Operators</t>
+  </si>
+  <si>
+    <t>All logging workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform logging work in roles not classified separately. | Attach chokers, cables, and rigging to logs for yarding operations. | Signal equipment operators to guide the movement of logs and machinery. | Cut, limb, and buck trees using chain saws and hand tools. | Operate skidders, loaders, and yarding equipment to move timber. | Sort, stack, and mark logs according to species, grade, and destination. | Clear brush, debris, and obstructions from landings and skid trails. | Inspect and maintain saws, cables, rigging, and safety equipment. | Follow safety procedures for falling, rigging, and equipment operation. | Build and maintain access roads, landings, and stream crossings. | Measure and record log dimensions, volumes, and load counts. | Assist with loading logs onto trucks and securing loads for transport. | Monitor weather and terrain conditions affecting safe operations. | Apply erosion control and site restoration measures after harvest.</t>
+  </si>
+  <si>
+    <t>47-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Construction Trades and Extraction Workers</t>
+  </si>
+  <si>
+    <t>Coal Mine Production Foreman | Construction Foreman | Construction Supervisor | Electrical Supervisor | Field Operations Supervisor | Field Supervisor | Insulation Foreman | Roustabout Field Supervisor | Sheet Metal Foreman | Site Superintendent</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Autodesk AutoCAD | FranklinCovey TabletPlanner | Graphics software | HCSS HeavyJob | Inventory tracking software | Mi-Co Mi-Forms | Microsoft Excel | Microsoft NetMeeting | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera P6 Enterprise Portfolio Project Management | Oracle Primavera Systems | Procore software | Prolog | QuickBase business management software | Sage 300 Construction and Real Estate | Scheduling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension | Monitoring | Learning Strategies | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Administration and Management | Building and Construction | Mechanical | Customer and Personal Service | English Language | Design | Public Safety and Security | Mathematics | Engineering and Technology | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Information Ordering | Near Vision | Deductive Reasoning | Speech Clarity | Written Comprehension | Inductive Reasoning | Written Expression | Speech Recognition | Far Vision | Manual Dexterity | Selective Attention | Control Precision | Finger Dexterity | Time Sharing | Visualization | Perceptual Speed | Mathematical Reasoning | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Telephone Conversations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | E-Mail | Work Outcomes and Results of Other Workers | Outdoors, Exposed to All Weather Conditions | Importance of Being Exact or Accurate | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Contaminants | Physical Proximity | Deal With External Customers or the Public in General | Conflict Situations | Written Letters and Memos | Level of Competition | Spend Time Standing | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Civil Engineering Technologists and Technicians | Construction Managers | Construction and Building Inspectors | Electricians | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Helpers--Electricians | Industrial Engineers | Maintenance and Repair Workers, General | Solar Energy Installation Managers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of construction or extraction workers.</t>
+  </si>
+  <si>
+    <t>Analyze worker or production problems and recommend solutions, such as improving production methods or implementing motivational plans. | Arrange for repairs of equipment or machinery. | Assign work to employees, based on material or worker requirements of specific jobs. | Confer with managerial or technical personnel, other departments, or contractors to resolve problems or to coordinate activities. | Coordinate work activities with other construction project activities. | Estimate material or worker requirements to complete jobs. | Inspect work progress, equipment, or construction sites to verify safety or to ensure that specifications are met. | Locate, measure, and mark site locations or placement of structures or equipment, using measuring and marking equipment. | Order or requisition materials or supplies. | Provide assistance to workers engaged in construction or extraction activities, using hand tools or other equipment. | Read specifications, such as blueprints, to determine construction requirements or to plan procedures. | Record information, such as personnel, production, or operational data on specified forms or reports. | Suggest or initiate personnel actions, such as promotions, transfers, or hires. | Supervise, coordinate, or schedule the activities of construction or extractive workers. | Train workers in construction methods, operation of equipment, safety procedures, or company policies.</t>
+  </si>
+  <si>
+    <t>47-1011.03</t>
+  </si>
+  <si>
+    <t>Solar Energy Installation Managers</t>
+  </si>
+  <si>
+    <t>Commercial Field Manager | Commercial Solar Superintendent | Installation Manager | Residential Field Manager | Residential Field Supervisor | Solar Energy Installation Manager | Solar Field Supervisor | Solar Installation Crew Foreman | Solar Installation Manager | Solar Installation Supervisor</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley STAAD | Computer aided design and drafting software CADD | Cost estimating software | Esri ArcGIS | Inventory tracking software | Mapping software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PVsyst | Procore software | Prolog | Real time operating system RTOS software | SAP software | Salesforce software | Trimble SketchUp Pro | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Speaking | Active Listening | Critical Thinking | Learning Strategies | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | Administration and Management | Design | Mechanical | Transportation | Sales and Marketing | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Written Comprehension | Problem Sensitivity | Deductive Reasoning | Near Vision | Information Ordering | Inductive Reasoning | Written Expression | Visualization | Far Vision | Speech Clarity | Speech Recognition | Arm-Hand Steadiness | Control Precision | Manual Dexterity | Visual Color Discrimination | Selective Attention | Flexibility of Closure | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Contact With Others | E-Mail | Telephone Conversations | Frequency of Decision Making | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Time Pressure | Health and Safety of Other Workers | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Deal With External Customers or the Public in General | Spend Time Standing | Exposed to High Places | Exposed to Hazardous Conditions | Level of Competition | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Importance of Repeating Same Tasks | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Architects, Except Landscape and Naval | Civil Engineers | Construction Managers | Construction and Building Inspectors | Electrical Engineers | Electricians | Energy Auditors | Energy Engineers, Except Wind and Solar | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Mechanics, Installers, and Repairers | Geothermal Production Managers | Industrial Engineers | Maintenance and Repair Workers, General | Project Management Specialists | Solar Energy Systems Engineers | Solar Photovoltaic Installers | Solar Sales Representatives and Assessors | Solar Thermal Installers and Technicians | Weatherization Installers and Technicians | Wind Energy Development Managers</t>
+  </si>
+  <si>
+    <t>Direct work crews installing residential or commercial solar photovoltaic or thermal systems.</t>
+  </si>
+  <si>
+    <t>Assess potential solar installation sites to determine feasibility and design requirements. | Assess system performance or functionality at the system, subsystem, and component levels. | Coordinate or schedule building inspections for solar installation projects. | Develop and maintain system architecture, including all piping, instrumentation, or process flow diagrams. | Estimate materials, equipment, and personnel needed for residential or commercial solar installation projects. | Evaluate subcontractors or subcontractor bids for quality, cost, and reliability. | Identify means to reduce costs, minimize risks, or increase efficiency of solar installation projects. | Monitor work of contractors and subcontractors to ensure projects conform to plans, specifications, schedules, or budgets. | Perform start-up of systems for testing or customer implementation. | Plan and coordinate installations of photovoltaic (PV) solar and solar thermal systems to ensure conformance to codes. | Prepare solar installation project proposals, quotes, budgets, or schedules. | Provide technical assistance to installers, technicians, or other solar professionals in areas such as solar electric systems, solar thermal systems, electrical systems, or mechanical systems. | Purchase or rent equipment for solar energy system installation. | Supervise solar installers, technicians, and subcontractors for solar installation projects to ensure compliance with safety standards. | Visit customer sites to determine solar system needs, requirements, or specifications.</t>
+  </si>
+  <si>
+    <t>47-2011.00</t>
+  </si>
+  <si>
+    <t>Boilermakers</t>
+  </si>
+  <si>
+    <t>Boiler Installer | Boiler Mechanic | Boiler Repairman | Boiler Service Technician (Boiler Service Tech) | Boiler Technician (Boiler Tech) | Boilermaker | Boilermaker Mechanic | Boilermaker Pipe Fitter | Boilermaker Welder | Industrial Boiler Service Technician (Industrial Boiler Service Tech)</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Health and safety training software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Mathematics</t>
+  </si>
+  <si>
+    <t>Control Precision | Near Vision | Problem Sensitivity | Deductive Reasoning | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Multilimb Coordination | Inductive Reasoning | Oral Comprehension | Speech Clarity | Auditory Attention | Far Vision | Extent Flexibility | Trunk Strength | Static Strength | Reaction Time | Selective Attention | Visualization | Perceptual Speed | Flexibility of Closure | Category Flexibility | Information Ordering | Fluency of Ideas | Written Expression | Oral Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Freedom to Make Decisions | Spend Time Standing | Time Pressure | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Determine Tasks, Priorities and Goals | Indoors, Not Environmentally Controlled | Deal With External Customers or the Public in General | Work Outcomes and Results of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Plumbers, Pipefitters, and Steamfitters | Sheet Metal Workers | Stationary Engineers and Boiler Operators | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Construct, assemble, maintain, and repair stationary steam boilers and boiler house auxiliaries. Align structures or plate sections to assemble boiler frame tanks or vats, following blueprints. Work involves use of hand and power tools, plumb bobs, levels, wedges, dogs, or turnbuckles. Assist in testing assembled vessels. Direct cleaning of boilers and boiler furnaces. Inspect and repair boiler fittings, such as safety valves, regulators, automatic-control mechanisms, water columns, and auxiliary machines.</t>
+  </si>
+  <si>
+    <t>Assemble large vessels in an on-site fabrication shop prior to installation to ensure proper fit. | Attach rigging and signal crane or hoist operators to lift heavy frame and plate sections or other parts into place. | Bell, bead with power hammers, or weld pressure vessel tube ends to ensure leakproof joints. | Bolt or arc weld pressure vessel structures and parts together, using wrenches or welding equipment. | Clean pressure vessel equipment, using scrapers, wire brushes, and cleaning solvents. | Conduct pressure tests on vessels, such as boilers. | Examine boilers, pressure vessels, tanks, or vats to locate defects, such as leaks, weak spots, or defective sections, so that they can be repaired. | Inspect assembled vessels or individual components, such as tubes, fittings, valves, controls, or auxiliary mechanisms, to locate any defects. | Install manholes, handholes, taps, tubes, valves, gauges, or feedwater connections in drums of water tube boilers, using hand tools. | Install refractory bricks or other heat-resistant materials in fireboxes of pressure vessels. | Lay out plate, sheet steel, or other heavy metal and locate and mark bending and cutting lines, using protractors, compasses, and drawing instruments or templates. | Locate and mark reference points for columns or plates on boiler foundations, following blueprints and using straightedges, squares, transits, or measuring instruments. | Position, align, and secure structural parts or related assemblies to boiler frames, tanks, or vats of pressure vessels, following blueprints. | Repair or replace defective pressure vessel parts, such as safety valves or regulators, using torches, jacks, caulking hammers, power saws, threading dies, welding equipment, or metalworking machinery. | Shape or fabricate parts, such as stacks, uptakes, or chutes, to adapt pressure vessels, heat exchangers, or piping to premises, using heavy-metalworking machines such as brakes, rolls, or drill presses. | Shape seams, joints, or irregular edges of pressure vessel sections or structural parts to attain specified fit of parts, using cutting torches, hammers, files, or metalworking machines. | Straighten or reshape bent pressure vessel plates or structure parts, using hammers, jacks, or torches. | Study blueprints to determine locations, relationships, or dimensions of parts.</t>
+  </si>
+  <si>
+    <t>47-2021.00</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons</t>
+  </si>
+  <si>
+    <t>Block Layer | Block Mason | Blockmason | Brick Mason | Brick and Block Mason | Bricklayer | Mason | Masonry Installer | Tender</t>
+  </si>
+  <si>
+    <t>CPR Visual Estimator | Construction Management Software ProEst | Daystar iStructural.com | Estimating software | Intuit QuickBooks | Microsoft Excel | Microsoft Office software | Microsoft Windows | RISA Technologies RISA-3D | Tradesman's Software Master Estimator</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mathematics | English Language | Public Safety and Security | Production and Processing | Design | Administration and Management | Mechanical</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Extent Flexibility | Near Vision | Arm-Hand Steadiness | Manual Dexterity | Static Strength | Visualization | Multilimb Coordination | Dynamic Strength | Information Ordering | Finger Dexterity | Problem Sensitivity | Gross Body Equilibrium | Far Vision | Gross Body Coordination | Stamina | Control Precision | Selective Attention | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Oral Expression | Oral Comprehension | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Exposed to Hazardous Equipment | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Physical Proximity | Exposed to High Places | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Spend Time Climbing Ladders, Scaffolds, or Poles | Telephone Conversations | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Contact With Others | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Frequency of Decision Making | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Extremely Bright or Inadequate Lighting Conditions | Impact of Decisions on Co-workers or Company Results | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection</t>
+  </si>
+  <si>
+    <t>Boilermakers | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Plasterers and Stucco Masons | Refractory Materials Repairers, Except Brickmasons | Reinforcing Iron and Rebar Workers | Sheet Metal Workers | Stonemasons | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Lay and bind building materials, such as brick, structural tile, concrete block, cinder block, glass block, and terra-cotta block, with mortar and other substances, to construct or repair walls, partitions, arches, sewers, and other structures.</t>
+  </si>
+  <si>
+    <t>Apply and smooth mortar or other mixture over work surface. | Break or cut bricks, tiles, or blocks to size, using trowel edge, hammer, or power saw. | Calculate angles and courses and determine vertical and horizontal alignment of courses. | Clean working surface to remove scale, dust, soot, or chips of brick and mortar, using broom, wire brush, or scraper. | Construct corners by fastening in plumb position a corner pole or building a corner pyramid of bricks, and filling in between the corners using a line from corner to corner to guide each course, or layer, of brick. | Examine brickwork or structure to determine need for repair. | Fasten or fuse brick or other building material to structure with wire clamps, anchor holes, torch, or cement. | Interpret blueprints and drawings to determine specifications and to calculate the materials required. | Lay and align bricks, blocks, or tiles to build or repair structures or high temperature equipment, such as cupola, kilns, ovens, or furnaces. | Measure distance from reference points and mark guidelines to lay out work, using plumb bobs and levels. | Mix specified amounts of sand, clay, dirt, or mortar powder with water to form refractory mixtures. | Remove burned or damaged brick or mortar, using sledgehammer, crowbar, chipping gun, or chisel. | Remove excess mortar with trowels and hand tools, and finish mortar joints with jointing tools, for a sealed, uniform appearance. | Spray or spread refractory material over brickwork to protect against deterioration.</t>
+  </si>
+  <si>
+    <t>47-2022.00</t>
+  </si>
+  <si>
+    <t>Stonemasons</t>
+  </si>
+  <si>
+    <t>Marble Installer | Marble Shop Worker | Mason | Mason Mechanic | Stone Derrickman | Stone Installer | Stone Mason | Stone Setter | Stonemason</t>
+  </si>
+  <si>
+    <t>CPR Visual Estimator | Citrix cloud computing software | Gregg Software Gregg Rock-It | Intuit QuickBooks | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Word | ProEst Software ProEst Estimating | RISA Technologies RISA-3D | SAP software | Tradesman&amp;apos;s Software Master Estimator | Virtual private networking VPN software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Monitoring | Mathematics | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Design | Mathematics | Mechanical | Customer and Personal Service | Administration and Management | English Language</t>
+  </si>
+  <si>
+    <t>Static Strength | Trunk Strength | Near Vision | Arm-Hand Steadiness | Manual Dexterity | Problem Sensitivity | Visualization | Stamina | Far Vision | Extent Flexibility | Multilimb Coordination | Information Ordering | Oral Comprehension | Selective Attention | Finger Dexterity | Dynamic Strength | Category Flexibility | Deductive Reasoning | Gross Body Equilibrium | Control Precision | Oral Expression | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Frequency of Decision Making | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Telephone Conversations | Exposed to Hazardous Equipment | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Contact With Others | Deal With External Customers or the Public in General | Spend Time Making Repetitive Motions | Physical Proximity | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Consequence of Error | Time Pressure</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Molders, Shapers, and Casters, Except Metal and Plastic | Plasterers and Stucco Masons | Refractory Materials Repairers, Except Brickmasons | Reinforcing Iron and Rebar Workers | Roofers | Segmental Pavers | Stone Cutters and Carvers, Manufacturing | Structural Iron and Steel Workers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Build stone structures, such as piers, walls, and abutments. Lay walks, curbstones, or special types of masonry for vats, tanks, and floors.</t>
+  </si>
+  <si>
+    <t>Clean excess mortar or grout from surface of marble, stone, or monument, using sponge, brush, water, or acid. | Construct and install prefabricated masonry units. | Dig trench for foundation of monument, using pick and shovel. | Drill holes in marble or ornamental stone and anchor brackets in holes. | Lay brick to build shells of chimneys and smokestacks or to line or reline industrial furnaces, kilns, boilers and similar installations. | Lay out wall patterns or foundations, using straight edge, rule, or staked lines. | Mix mortar or grout and pour or spread mortar or grout on marble slabs, stone, or foundation. | Position mold along guidelines of wall, press mold in place, and remove mold and paper from wall. | Remove sections of monument from truck bed, and guide stone onto foundation, using skids, hoist, or truck crane. | Remove wedges, fill joints between stones, finish joints between stones, using a trowel, and smooth the mortar to an attractive finish, using a tuck pointer. | Repair cracked or chipped areas of stone or marble, using blowtorch and mastic, and remove rough or defective spots from concrete, using power grinder or chisel and hammer. | Replace broken or missing masonry units in walls or floors. | Set stone or marble in place, according to layout or pattern. | Set vertical and horizontal alignment of structures, using plumb bob, gauge line, and level. | Shape, trim, face and cut marble or stone preparatory to setting, using power saws, cutting equipment, and hand tools. | Smooth, polish, and bevel surfaces, using hand tools and power tools.</t>
+  </si>
+  <si>
+    <t>47-2031.00</t>
+  </si>
+  <si>
+    <t>Carpenters</t>
+  </si>
+  <si>
+    <t>Bridge Carpenter | Cabinet Maker | Carpenter | Concrete Carpenter | Construction Carpenter | Form Carpenter | Framer | Maintenance Carpenter | Rough Carpenter | Scaffold Builder</t>
+  </si>
+  <si>
+    <t>Bosch Punch List | Craftsman CD Estimator | Drawing and drafting software | Estimating software | Intuit QuickBooks | Job costing software | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | Quicken | Renaissance MasterCarpenter | Turtle Creek Software Goldenseal | VirtualBoss | Web browser software | Wilhelm Publishing Threshold</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Reading Comprehension | Speaking | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mathematics | Administration and Management | Design | Engineering and Technology | Public Safety and Security | Mechanical | Education and Training | Customer and Personal Service | Physics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Visualization | Near Vision | Manual Dexterity | Finger Dexterity | Trunk Strength | Arm-Hand Steadiness | Information Ordering | Deductive Reasoning | Far Vision | Multilimb Coordination | Oral Expression | Oral Comprehension | Static Strength | Inductive Reasoning | Reaction Time | Control Precision | Selective Attention | Category Flexibility | Speech Clarity | Speech Recognition | Explosive Strength | Perceptual Speed | Flexibility of Closure | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Standing | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Time Pressure | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work Outcomes and Results of Other Workers | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Physical Proximity | Consequence of Error | Exposed to Hazardous Equipment | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Spend Time Bending or Twisting Your Body | Exposed to High Places</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Brickmasons and Blockmasons | Cabinetmakers and Bench Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Layout Workers, Metal and Plastic | Plasterers and Stucco Masons | Reinforcing Iron and Rebar Workers | Roofers | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Construct, erect, install, or repair structures and fixtures made of wood and comparable materials, such as concrete forms; building frameworks, including partitions, joists, studding, and rafters; and wood stairways, window and door frames, and hardwood floors. May also install cabinets, siding, drywall, and batt or roll insulation. Includes brattice builders who build doors or brattices (ventilation walls or partitions) in underground passageways.</t>
+  </si>
+  <si>
+    <t>Anchor and brace forms and other structures in place, using nails, bolts, anchor rods, steel cables, planks, wedges, and timbers. | Apply shock-absorbing, sound-deadening, or decorative paneling to ceilings or walls. | Arrange for subcontractors to deal with special areas, such as heating or electrical wiring work. | Assemble and fasten materials to make frameworks or props, using hand tools and wood screws, nails, dowel pins, or glue. | Bore boltholes in timber, masonry or concrete walls, using power drill. | Build or repair cabinets, doors, frameworks, floors, or other wooden fixtures used in buildings, using woodworking machines, carpenter's hand tools, or power tools. | Build sleds from logs and timbers for use in hauling camp buildings and machinery through wooded areas. | Construct forms or chutes for pouring concrete. | Cover subfloors with building paper to keep out moisture and lay hardwood, parquet, or wood-strip-block floors by nailing floors to subfloor or cementing them to mastic or asphalt base. | Dig or direct digging of post holes and set poles to support structures. | Erect scaffolding or ladders for assembling structures above ground level. | Examine structural timbers and supports to detect decay, and replace timbers as required, using hand tools, nuts, and bolts. | Fill cracks or other defects in plaster or plasterboard and sand patch, using patching plaster, trowel, and sanding tool. | Finish surfaces of woodwork or wallboard in houses or buildings, using paint, hand tools, or paneling. | Follow established safety rules and regulations and maintain a safe and clean environment. | Inspect ceiling or floor tile, wall coverings, siding, glass, or woodwork to detect broken or damaged structures. | Install rough door and window frames, subflooring, fixtures, or temporary supports in structures undergoing construction or repair. | Install structures or fixtures, such as windows, frames, floorings, trim, or hardware, using carpenters' hand or power tools. | Maintain job records and schedule work crew. | Maintain records, document actions, and present written progress reports. | Measure and mark cutting lines on materials, using a ruler, pencil, chalk, and marking gauge. | Perform minor plumbing, welding, or concrete mixing work. | Prepare cost estimates for clients or employers. | Remove damaged or defective parts or sections of structures and repair or replace, using hand tools. | Select and order lumber or other required materials. | Shape or cut materials to specified measurements, using hand tools, machines, or power saws. | Study specifications in blueprints, sketches, or building plans to prepare project layout and determine dimensions and materials required. | Verify trueness of structure, using plumb bob and level. | Work with or remove hazardous material.</t>
+  </si>
+  <si>
+    <t>47-2041.00</t>
+  </si>
+  <si>
+    <t>Carpet Installers</t>
+  </si>
+  <si>
+    <t>Carpet Installer | Carpet Layer | Carpet Mechanic | Commercial Floor Covering Installer | Floor Coverer | Floor Covering Installer | Floor Installation Mechanic | Flooring Installer | Installer</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Aya Associates Comp-U-Floor | Carpet Dealer Management System CDMS | FIRST Flooring | FloorCOST Estimator for Excel | Flooring Technologies QFloors | Focus Floor Covering Software | Measure Square FloorEstimate Pro | Microsoft Excel | Microsoft Office software | Microsoft Word | Pacific Solutions FloorRight | RFMS Schedule Pro | Textile Management Systems RollMaster | eTakeoff</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mathematics | Administration and Management | English Language | Building and Construction | Production and Processing</t>
+  </si>
+  <si>
+    <t>Extent Flexibility | Trunk Strength | Problem Sensitivity | Near Vision | Static Strength | Speech Recognition | Visualization | Arm-Hand Steadiness | Manual Dexterity | Oral Expression | Stamina | Multilimb Coordination | Finger Dexterity | Depth Perception | Far Vision | Dynamic Strength | Selective Attention | Information Ordering | Deductive Reasoning | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Kneeling, Crouching, Stooping, or Crawling | Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Time Pressure | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Exposed to Cramped Work Space, Awkward Positions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Furniture Finishers | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Paperhangers | Plasterers and Stucco Masons | Roofers | Segmental Pavers | Stone Cutters and Carvers, Manufacturing | Terrazzo Workers and Finishers | Tile and Stone Setters | Upholsterers</t>
+  </si>
+  <si>
+    <t>Lay and install carpet from rolls or blocks on floors. Install padding and trim flooring materials.</t>
+  </si>
+  <si>
+    <t>Clean up before and after installation, including vacuuming carpet and discarding remnant pieces. | Cut and bind material. | Cut and trim carpet to fit along wall edges, openings, and projections, finishing the edges with a wall trimmer. | Cut carpet padding to size and install padding, following prescribed method. | Draw building diagrams and record dimensions. | Fasten metal treads across door openings or where carpet meets flooring to hold carpet in place. | Inspect the surface to be covered to determine its condition, and correct any imperfections that might show through carpet or cause carpet to wear unevenly. | Install carpet on some floors using adhesive, following prescribed method. | Join edges of carpet and seam edges where necessary, by sewing or by using tape with glue and heated carpet iron. | Measure, cut and install tackless strips along the baseboard or wall. | Move furniture from area to be carpeted and remove old carpet and padding. | Nail tack strips around area to be carpeted or use old strips to attach edges of new carpet. | Plan the layout of the carpet, allowing for expected traffic patterns and placing seams for best appearance and longest wear. | Roll out, measure, mark, and cut carpeting to size with a carpet knife, following floor sketches and allowing extra carpet for final fitting. | Stretch carpet to align with walls and ensure a smooth surface, and press carpet in place over tack strips or use staples, tape, tacks or glue to hold carpet in place. | Take measurements and study floor sketches to calculate the area to be carpeted and the amount of material needed.</t>
+  </si>
+  <si>
+    <t>47-2042.00</t>
+  </si>
+  <si>
+    <t>Floor Layers, Except Carpet, Wood, and Hard Tiles</t>
+  </si>
+  <si>
+    <t>Floor Covering Contractor | Floor Coverings Installer | Floor Layer | Flooring Installer | Flooring Mechanic | Tile Installer | Tile Setter | Vinyl Installer</t>
+  </si>
+  <si>
+    <t>Aya Associates Comp-U-Floor | CPR Software FloorCOST Estimator for Excel | Facebook | Flooring Technologies QFloors | Focus Floor Covering Software | Measure Square FloorEstimate Pro | Microsoft Office software | On Center On-Screen Takeoff | Pacific Solutions FloorRight | Project visualization software | Radio frequency identification RFID software | Textile Management Systems RollMaster | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | Mathematics | Mechanical | Production and Processing | Design</t>
+  </si>
+  <si>
+    <t>Near Vision | Extent Flexibility | Arm-Hand Steadiness | Oral Comprehension | Static Strength | Finger Dexterity | Manual Dexterity | Problem Sensitivity | Oral Expression | Speech Clarity | Information Ordering | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Spend Time Kneeling, Crouching, Stooping, or Crawling | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Telephone Conversations | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Frequency of Decision Making | Exposed to Cramped Work Space, Awkward Positions | Indoors, Environmentally Controlled | Physical Proximity | Exposed to Hazardous Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Floor Sanders and Finishers | Furniture Finishers | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Paperhangers | Plasterers and Stucco Masons | Roofers | Segmental Pavers | Sheet Metal Workers | Stone Cutters and Carvers, Manufacturing | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Apply blocks, strips, or sheets of shock-absorbing, sound-deadening, or decorative coverings to floors.</t>
+  </si>
+  <si>
+    <t>Apply adhesive cement to floor or wall material to join and adhere foundation material. | Cut covering and foundation materials, according to blueprints and sketches. | Cut flooring material to fit around obstructions. | Determine traffic areas and decide location of seams. | Disconnect and remove appliances, light fixtures, and worn floor and wall covering from floors, walls, and cabinets. | Form a smooth foundation by stapling plywood or Masonite over the floor or by brushing waterproof compound onto surface and filling cracks with plaster, putty, or grout to seal pores. | Heat and soften floor covering materials to patch cracks or fit floor coverings around irregular surfaces, using blowtorch. | Inspect surface to be covered to ensure that it is firm and dry. | Lay out, position, and apply shock-absorbing, sound-deadening, or decorative coverings to floors, walls, and cabinets, following guidelines to keep courses straight and create designs. | Measure and mark guidelines on surfaces or foundations, using chalk lines and dividers. | Remove excess cement to clean finished surface. | Roll and press sheet wall and floor covering into cement base to smooth and finish surface, using hand roller. | Sweep, scrape, sand, or chip dirt and irregularities to clean base surfaces, correcting imperfections that may show through the covering. | Trim excess covering materials, tack edges, and join sections of covering material to form tight joint.</t>
+  </si>
+  <si>
+    <t>47-2043.00</t>
+  </si>
+  <si>
+    <t>Floor Sanders and Finishers</t>
+  </si>
+  <si>
+    <t>Finisher | Floor Finisher | Floor Mechanic | Floor Refinisher | Floor Sander | Floor Sander and Finisher | Hardwood Floor Finisher and Sander | Hardwood Floor Refinisher | Hardwood Floor Sander | Sander</t>
+  </si>
+  <si>
+    <t>Floor planning software | FloorCOST Estimator for Excel | Flooring Technologies QFloors | Measure Square | Microsoft Excel | Pacific Solutions FloorRight | Vimeo</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | English Language | Production and Processing | Administration and Management | Mechanical</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Control Precision | Multilimb Coordination | Trunk Strength | Finger Dexterity | Stamina | Near Vision | Static Strength | Oral Comprehension | Extent Flexibility | Dynamic Strength | Reaction Time | Selective Attention | Oral Expression</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Bending or Twisting Your Body | Spend Time Making Repetitive Motions | Spend Time Kneeling, Crouching, Stooping, or Crawling | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Spend Time Walking or Running | Spend Time Standing | Frequency of Decision Making | Exposed to Hazardous Equipment | Work Outcomes and Results of Other Workers | Time Pressure | Contact With Others | Telephone Conversations | Exposed to Whole Body Vibration | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Furniture Finishers | Grinding and Polishing Workers, Hand | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Molders, Shapers, and Casters, Except Metal and Plastic | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Plasterers and Stucco Masons | Tapers | Terrazzo Workers and Finishers | Tile and Stone Setters | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Scrape and sand wooden floors to smooth surfaces using floor scraper and floor sanding machine, and apply coats of finish.</t>
+  </si>
+  <si>
+    <t>Apply filler compound and coats of finish to floors to seal wood. | Attach sandpaper to rollers of sanding machines. | Buff and vacuum floors to ensure their cleanliness prior to the application of finish. | Guide sanding machines over surfaces of floors until surfaces are smooth. | Inspect floors for smoothness. | Remove excess glue from joints, using knives, scrapers, or wood chisels. | Scrape and sand floor edges and areas inaccessible to floor sanders, using scrapers, disk-type sanders, and sandpaper.</t>
+  </si>
+  <si>
+    <t>47-2044.00</t>
+  </si>
+  <si>
+    <t>Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Ceramic Tile Mechanic | Ceramic Tile Setter | Tile Finisher | Tile Installer | Tile Man | Tile Mason | Tile Mechanic | Tile Setter | Tile and Marble Installer | Tile and Marble Setter</t>
+  </si>
+  <si>
+    <t>Aya Associates Comp-U-Floor | EasyCAD Iris 2D | Measure Square FloorEstimate Pro | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Salesforce software | TileGem</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Mathematics | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mathematics | Customer and Personal Service | Design</t>
+  </si>
+  <si>
+    <t>Visualization | Near Vision | Extent Flexibility | Trunk Strength | Problem Sensitivity | Information Ordering | Far Vision | Stamina | Static Strength | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Category Flexibility | Oral Comprehension | Speech Clarity | Speech Recognition | Visual Color Discrimination | Control Precision | Inductive Reasoning | Deductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Making Repetitive Motions | Spend Time Bending or Twisting Your Body | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Spend Time Standing | Determine Tasks, Priorities and Goals | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Time Pressure | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Furniture Finishers | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Paperhangers | Plasterers and Stucco Masons | Roofers | Segmental Pavers | Stone Cutters and Carvers, Manufacturing | Stonemasons | Terrazzo Workers and Finishers</t>
+  </si>
+  <si>
+    <t>Apply hard tile, stone, and comparable materials to walls, floors, ceilings, countertops, and roof decks.</t>
+  </si>
+  <si>
+    <t>Align and straighten tile using levels, squares, and straightedges. | Apply a sealer to make grout stain- and water-resistant. | Apply mortar to tile back, position the tile, and press or tap with trowel handle to affix tile to base. | Assist customers in selection of tile and grout. | Brush glue onto manila paper on which design has been drawn and position tiles, finished side down, onto paper. | Build underbeds and install anchor bolts, wires, and brackets. | Cut and shape tile to fit around obstacles and into odd spaces and corners, using hand and power cutting tools. | Cut tile backing to required size, using shears. | Cut, surface, polish, and install marble and granite or install pre-cast terrazzo, granite or marble units. | Determine and implement the best layout to achieve a desired pattern. | Finish and dress the joints and wipe excess grout from between tiles, using damp sponge. | Install and anchor fixtures in designated positions, using hand tools. | Lay and set mosaic tiles to create decorative wall, mural, and floor designs. | Level concrete and allow to dry. | Measure and cut metal lath to size for walls and ceilings, using tin snips. | Measure and mark surfaces to be tiled, following blueprints. | Mix and apply mortar or cement to edges and ends of drain tiles to seal halves and joints. | Mix, apply, and spread plaster, concrete, mortar, cement, mastic, glue or other adhesives to form a bed for the tiles, using brush, trowel and screed. | Prepare cost and labor estimates, based on calculations of time and materials needed for project. | Prepare surfaces for tiling by attaching lath or waterproof paper, or by applying a cement mortar coat to a metal screen. | Remove and replace cracked or damaged tile. | Remove any old tile, grout and adhesive using chisels and scrapers and clean the surface carefully. | Select and order tile and other items to be installed, such as bathroom accessories, walls, panels, and cabinets, according to specifications. | Spread mastic or other adhesive base on roof deck to form base for promenade tile, using serrated spreader. | Study blueprints and examine surface to be covered to determine amount of material needed.</t>
+  </si>
+  <si>
+    <t>47-2051.00</t>
+  </si>
+  <si>
+    <t>Cement Masons and Concrete Finishers</t>
+  </si>
+  <si>
+    <t>Cement Finisher | Cement Mason | Concrete Finisher | Concrete Mason | Finisher | Mason</t>
+  </si>
+  <si>
+    <t>ACT Contractors Forms | ADAPT-Modeler | HIPERPAV | Hard Dollar HD Project Estimating | LogicSphere Firstmix | Maxwell Systems Quest Estimator | National Concrete &amp; Masonry Estimator | Shilstone seeMIX | Sirus GT Construction Accounting | Tradesman's Software Master Estimator</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>English Language | Building and Construction | Mathematics | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Trunk Strength | Multilimb Coordination | Near Vision | Arm-Hand Steadiness | Control Precision | Extent Flexibility | Dynamic Strength | Stamina | Problem Sensitivity | Deductive Reasoning | Information Ordering | Visualization | Category Flexibility | Oral Expression | Oral Comprehension | Speech Recognition | Far Vision | Static Strength | Finger Dexterity | Selective Attention | Speech Clarity | Depth Perception | Gross Body Coordination | Reaction Time | Rate Control | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Physical Proximity | Spend Time Walking or Running | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Spend Time Bending or Twisting Your Body | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Contact With Others | Exposed to Hazardous Equipment | Spend Time Kneeling, Crouching, Stooping, or Crawling | Time Pressure | Impact of Decisions on Co-workers or Company Results | In an Open Vehicle or Operating Equipment | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Foundry Mold and Coremakers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Molders, Shapers, and Casters, Except Metal and Plastic | Paving, Surfacing, and Tamping Equipment Operators | Plasterers and Stucco Masons | Refractory Materials Repairers, Except Brickmasons | Reinforcing Iron and Rebar Workers | Roofers | Segmental Pavers | Stonemasons | Structural Iron and Steel Workers | Tapers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Smooth and finish surfaces of poured concrete, such as floors, walks, sidewalks, roads, or curbs using a variety of hand and power tools. Align forms for sidewalks, curbs, or gutters; patch voids; and use saws to cut expansion joints.</t>
+  </si>
+  <si>
+    <t>Apply hardening and sealing compounds to cure surface of concrete, and waterproof or restore surface. | Apply muriatic acid to clean surface, and rinse with water. | Build wooden molds, and clamp molds around area to be repaired, using hand tools. | Check the forms that hold the concrete to see that they are properly constructed. | Chip, scrape, and grind high spots, ridges, and rough projections to finish concrete, using pneumatic chisels, power grinders, or hand tools. | Clean chipped area, using wire brush, and feel and observe surface to determine if it is rough or uneven. | Cut metal division strips, and press them into terrazzo base so that top edges form desired design or pattern. | Cut out damaged areas, drill holes for reinforcing rods, and position reinforcing rods to repair concrete, using power saw and drill. | Direct the casting of the concrete and supervise laborers who use shovels or special tools to spread it. | Fabricate concrete beams, columns, and panels. | Install anchor bolts, steel plates, door sills and other fixtures in freshly poured concrete or pattern or stamp the surface to provide a decorative finish. | Mix cement, sand, and water to produce concrete, grout, or slurry, using hoe, trowel, tamper, scraper, or concrete-mixing machine. | Mold expansion joints and edges, using edging tools, jointers, and straightedge. | Monitor how the wind, heat, or cold affect the curing of the concrete throughout the entire process. | Operate power vibrator to compact concrete. | Polish surface, using polishing or surfacing machine. | Produce rough concrete surface, using broom. | Push roller over surface to embed chips in surface. | Set the forms that hold concrete to the desired pitch and depth, and align them. | Signal truck driver to position truck to facilitate pouring concrete, and move chute to direct concrete on forms. | Spread roofing paper on surface of foundation, and spread concrete onto roofing paper with trowel to form terrazzo base. | Spread, level, and smooth concrete, using rake, shovel, hand or power trowel, hand or power screed, and float. | Sprinkle colored marble or stone chips, powdered steel, or coloring powder over surface to produce prescribed finish. | Waterproof or restore concrete surfaces, using appropriate compounds. | Wet concrete surface, and rub with stone to smooth surface and obtain specified finish. | Wet surface to prepare for bonding, fill holes and cracks with grout or slurry, and smooth, using trowel.</t>
+  </si>
+  <si>
+    <t>47-2053.00</t>
+  </si>
+  <si>
+    <t>Terrazzo Workers and Finishers</t>
+  </si>
+  <si>
+    <t>Grinder | Installer | Terrazzo Finisher | Terrazzo Grinder | Terrazzo Installer | Terrazzo Journeyman | Terrazzo Laborer | Terrazzo Mechanic | Terrazzo Tile Setter | Terrazzo Worker</t>
+  </si>
+  <si>
+    <t>CPR International GeneralCOST Estimator | CPR Visual Estimator | Construction Management Software ProEst | Intuit QuickBooks | Microsoft Excel | Microsoft Windows | On Center Quick Bid | Sapro Systems Paymee</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Reading Comprehension | Speaking | Mathematics</t>
+  </si>
+  <si>
+    <t>Building and Construction | Design | Mathematics | English Language | Administration and Management | Customer and Personal Service | Chemistry | Mechanical | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Near Vision | Trunk Strength | Multilimb Coordination | Arm-Hand Steadiness | Far Vision | Finger Dexterity | Extent Flexibility | Stamina | Static Strength | Control Precision | Visualization | Problem Sensitivity | Visual Color Discrimination | Dynamic Strength | Selective Attention | Information Ordering</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Exposed to Contaminants | Health and Safety of Other Workers | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Physical Proximity | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Foundry Mold and Coremakers | Furniture Finishers | Grinding and Polishing Workers, Hand | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Molders, Shapers, and Casters, Except Metal and Plastic | Plasterers and Stucco Masons | Refractory Materials Repairers, Except Brickmasons | Segmental Pavers | Stone Cutters and Carvers, Manufacturing | Stonemasons | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Apply a mixture of cement, sand, pigment, or marble chips to floors, stairways, and cabinet fixtures to fashion durable and decorative surfaces.</t>
+  </si>
+  <si>
+    <t>Blend marble chip mixtures, place into panels, and push a roller over the surface to embed the chips. | Build wooden molds, clamping molds around areas to be repaired, or setting up frames to the proper depth and alignment. | Chip, scrape, or grind high spots, ridges, or rough projections to finish concrete, using pneumatic chisel, hand chisel, or other hand tools. | Clean chipped area, using wire brush, and feel and observe surface to determine if it is rough or uneven. | Clean installation site, mixing and storage areas, tools, machines, and equipment, and store materials and equipment. | Cut metal division strips and press them into the terrazzo base for joints or changes of color to form designs or patterns or to help prevent cracks. | Fill slight grinding depressions with matching grout material and hand-trowel for a smooth, uniform surface. | Grind curved surfaces or areas inaccessible to surfacing machine, such as stairways or cabinet tops, with portable hand grinder. | Grind surfaces with a power grinder, or polish surfaces with polishing or surfacing machines. | Measure designated amounts of ingredients for terrazzo or grout, according to standard formulas and specifications, using graduated containers and scales, and load ingredients into portable mixer. | Mix cement, sand, and water to produce concrete, grout, or slurry, using hoe, trowel, tamper, scraper, or concrete-mixing machine. | Modify mixing, grouting, grinding, or cleaning procedures, according to type of installation or material used. | Mold expansion joints and edges, using edging tools, jointers, or straightedges. | Move terrazzo installation materials, tools, machines, or work devices to work areas, manually or using wheelbarrow. | Position and secure moisture membrane and wire mesh in preparation for pouring base materials for terrazzo installation. | Precast terrazzo blocks in wooden forms. | Produce rough concrete surface, using broom. | Remove frames when the foundation is dry. | Repair concrete by cutting out damaged areas, drilling holes for reinforcing rods, and positioning reinforcing rods, using power saw and drill. | Signal truck driver to position truck to facilitate pouring concrete and move chute to direct concrete on forms. | Spread roofing paper on surface of foundation and spread concrete onto roofing paper with trowel to form terrazzo base. | Spread, level, or smooth concrete or terrazzo mixtures to form bases or finished surfaces, using rakes, shovels, hand or power trowels, hand or power screeds, or floats. | Sprinkle colored marble or stone chips, powdered steel, or coloring powder over surface to produce prescribed finish. | Wash polished terrazzo surface, using cleaner and water, and apply sealer and curing agent according to manufacturer's specifications, using brush or sprayer. | Wet concrete surface and rub with stone to smooth surface and obtain specified finish. | Wet surface to prepare for bonding, fill holes and cracks with grout or slurry, and smooth with a trowel.</t>
+  </si>
+  <si>
+    <t>47-2061.00</t>
+  </si>
+  <si>
+    <t>Construction Laborers</t>
+  </si>
+  <si>
+    <t>Bituminous Asphalt Technician | Construction Laborer | Construction Worker | Drop Crew Laborer | Equipment Operator (EO) | Form Setter | Post Framer | Scaffolding Operator | Site Work Laborer | Toolman</t>
+  </si>
+  <si>
+    <t>Autodesk Revit | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Building and Construction | Public Safety and Security | Mechanical</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Static Strength | Multilimb Coordination | Arm-Hand Steadiness | Oral Comprehension | Oral Expression | Problem Sensitivity | Control Precision | Trunk Strength | Near Vision | Far Vision | Extent Flexibility | Stamina | Dynamic Strength | Finger Dexterity | Information Ordering | Speech Clarity | Speech Recognition | Depth Perception | Rate Control | Selective Attention | Category Flexibility | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Outdoors, Exposed to All Weather Conditions | Contact With Others | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment | Telephone Conversations | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Frequency of Decision Making | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Exposed to Extremely Bright or Inadequate Lighting Conditions | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Grinding and Polishing Workers, Hand | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Hoist and Winch Operators | Insulation Workers, Floor, Ceiling, and Wall | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Molders, Shapers, and Casters, Except Metal and Plastic | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pipelayers | Plumbers, Pipefitters, and Steamfitters | Segmental Pavers | Sheet Metal Workers | Structural Iron and Steel Workers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Perform tasks involving physical labor at construction sites. May operate hand and power tools of all types: air hammers, earth tampers, cement mixers, small mechanical hoists, surveying and measuring equipment, and a variety of other equipment and instruments. May clean and prepare sites, dig trenches, set braces to support the sides of excavations, erect scaffolding, and clean up rubble, debris, and other waste materials. May assist other craft workers.</t>
+  </si>
+  <si>
+    <t>Apply caulking compounds by hand or caulking guns to protect against entry of water or air. | Clean or prepare construction sites to eliminate possible hazards. | Control traffic passing near, in, or around work zones. | Dig ditches or trenches, backfill excavations, or compact and level earth to grade specifications, using picks, shovels, pneumatic tampers, or rakes. | Erect or dismantle scaffolding, shoring, braces, traffic barricades, ramps, or other temporary structures. | Grind, scrape, sand, or polish surfaces, such as concrete, marble, terrazzo, or wood flooring, using abrasive tools or machines. | Install sewer, water, or storm drain pipes, using pipe-laying machinery or laser guidance equipment. | Load, unload, or identify building materials, machinery, or tools, distributing them to the appropriate locations, according to project plans or specifications. | Lubricate, clean, or repair machinery, equipment, or tools. | Measure, mark, or record openings or distances to layout areas where construction work will be performed. | Mix ingredients to create compounds for covering or cleaning surfaces. | Mix, pour, or spread concrete, using portable cement mixers. | Mop, brush, or spread paints, cleaning solutions, or other compounds over surfaces to clean them or to provide protection. | Operate jackhammers or drills to break up concrete or pavement. | Operate or maintain air monitoring or other sampling devices in confined or hazardous environments. | Perform site activities required of green certified construction practices, such as implementing waste management procedures, identifying materials for reuse, or installing erosion or sedimentation control mechanisms. | Place, consolidate, or protect case-in-place concrete or masonry structures. | Position or dismantle forms for pouring concrete, using saws, hammers, nails, or bolts. | Position, join, align, or seal structural components, such as concrete wall sections or pipes. | Provide assistance to craft workers, such as carpenters, plasterers, or masons. | Raze buildings or salvage useful materials. | Read plans, instructions, or specifications to determine work activities. | Signal equipment operators to facilitate alignment, movement, or adjustment of machinery, equipment, or materials. | Smooth or finish freshly poured cement or concrete, using floats, trowels, screeds, or powered cement finishing tools. | Spray materials, such as water, sand, steam, vinyl, paint, or stucco, through hoses to clean, coat, or seal surfaces. | Tend machines that pump concrete, grout, cement, sand, plaster, or stucco through spray guns for application to ceilings or walls. | Tend pumps, compressors, or generators to provide power for tools, machinery, or equipment or to heat or move materials, such as asphalt.</t>
+  </si>
+  <si>
+    <t>47-2071.00</t>
+  </si>
+  <si>
+    <t>Paving, Surfacing, and Tamping Equipment Operators</t>
+  </si>
+  <si>
+    <t>Asphalt Paver Operator | Asphalt Paving Machine Operator | Asphalt Raker | Asphalt Roller Operator | Equipment Operator (EO) | Loader Operator | Maintenance Equipment Operator (MEO) | Paver Operator | Roller Operator | Screed Operator</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD Civil 3D | Database software | Email software | HCSS HeavyBid | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Time report software | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical</t>
+  </si>
+  <si>
+    <t>Control Precision | Problem Sensitivity | Multilimb Coordination | Rate Control | Reaction Time | Far Vision | Trunk Strength | Static Strength | Speech Clarity | Speech Recognition | Depth Perception | Arm-Hand Steadiness | Selective Attention | Visualization | Information Ordering | Deductive Reasoning | Oral Expression | Oral Comprehension | Extent Flexibility | Response Orientation | Manual Dexterity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | Exposed to Whole Body Vibration | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | In an Open Vehicle or Operating Equipment | Telephone Conversations | Exposed to Very Hot or Cold Temperatures | Exposed to Minor Burns, Cuts, Bites, or Stings | Physical Proximity | Spend Time Making Repetitive Motions | In an Enclosed Vehicle or Operate Enclosed Equipment | Pace Determined by Speed of Equipment | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Consequence of Error | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results | Spend Time Bending or Twisting Your Body | Exposed to Extremely Bright or Inadequate Lighting Conditions | Contact With Others</t>
+  </si>
+  <si>
+    <t>Cement Masons and Concrete Finishers | Construction Laborers | Continuous Mining Machine Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Grinding and Polishing Workers, Hand | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Pipelayers | Rail-Track Laying and Maintenance Equipment Operators | Roustabouts, Oil and Gas | Segmental Pavers | Terrazzo Workers and Finishers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate equipment used for applying concrete, asphalt, or other materials to road beds, parking lots, or airport runways and taxiways or for tamping gravel, dirt, or other materials. Includes concrete and asphalt paving machine operators, form tampers, tamping machine operators, and stone spreader operators.</t>
+  </si>
+  <si>
+    <t>Control paving machines to push dump trucks and to maintain a constant flow of asphalt or other material into hoppers or screeds. | Control traffic. | Coordinate truck dumping. | Cut or break up pavement and drive guardrail posts, using machines equipped with interchangeable hammers. | Drive and operate curbing machines to extrude concrete or asphalt curbing. | Drive machines onto truck trailers, and drive trucks to transport machines and material to and from job sites. | Fill tanks, hoppers, or machines with paving materials. | Inspect, clean, maintain, and repair equipment, using mechanics' hand tools, or report malfunctions to supervisors. | Install dies, cutters, and extensions to screeds onto machines, using hand tools. | Light burners or start heating units of machines, and regulate screed temperatures and asphalt flow rates. | Observe distribution of paving material to adjust machine settings or material flow, and indicate low spots for workers to add material. | Operate machines that clean or cut expansion joints in concrete or asphalt and that rout out cracks in pavement. | Operate machines to spread, smooth, level, or steel-reinforce stone, concrete, or asphalt on road beds. | Operate oil distributors, loaders, chip spreaders, dump trucks, and snow plows. | Operate tamping machines or manually roll surfaces to compact earth fills, foundation forms, and finished road materials, according to grade specifications. | Place strips of material, such as cork, asphalt, or steel into joints, or place rolls of expansion-joint material on machines that automatically insert material. | Set up and tear down equipment. | Set up forms and lay out guidelines for curbs, according to written specifications, using string, spray paint, and concrete or water mixes. | Shovel blacktop. | Start machine, engage clutch, and push and move levers to guide machine along forms or guidelines and to control the operation of machine attachments.</t>
+  </si>
+  <si>
+    <t>47-2072.00</t>
+  </si>
+  <si>
+    <t>Pile Driver Operators</t>
+  </si>
+  <si>
+    <t>Pile Driver | Pile Driver Operator | Pile Driving Operator</t>
+  </si>
+  <si>
+    <t>Email software | GRL Engineers Wave Equation Analysis Program GRLWEAP | Global positioning system GPS software | Microsoft Excel | Pile Dynamics Case Pile Wave Analysis Program CAPWAP | Pile Dynamics Pile Driving Analyzer PDA</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Mathematics | Transportation | Engineering and Technology | Public Safety and Security | Design</t>
+  </si>
+  <si>
+    <t>Control Precision | Depth Perception | Multilimb Coordination | Reaction Time | Manual Dexterity | Problem Sensitivity | Rate Control | Response Orientation | Selective Attention | Arm-Hand Steadiness | Deductive Reasoning | Speech Recognition | Far Vision | Visualization | Auditory Attention | Near Vision | Finger Dexterity | Spatial Orientation | Information Ordering | Inductive Reasoning | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Contact With Others | Exposed to Hazardous Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Consequence of Error | Exposed to Very Hot or Cold Temperatures | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Physical Proximity | In an Open Vehicle or Operating Equipment | Spend Time Making Repetitive Motions | Exposed to Whole Body Vibration | Time Pressure | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Construction Laborers | Continuous Mining Machine Operators | Crane and Tower Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Rail Car Repairers | Rail-Track Laying and Maintenance Equipment Operators | Riggers | Roustabouts, Oil and Gas | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Operate pile drivers mounted on skids, barges, crawler treads, or locomotive cranes to drive pilings for retaining walls, bulkheads, and foundations of structures such as buildings, bridges, and piers.</t>
+  </si>
+  <si>
+    <t>Clean, lubricate, and refill equipment. | Conduct pre-operational checks on equipment to ensure proper functioning. | Drive pilings to provide support for buildings or other structures, using heavy equipment with a pile driver head. | Move hand and foot levers of hoisting equipment to position piling leads, hoist piling into leads, and position hammers over pilings. | Move levers and turn valves to activate power hammers, or to raise and lower drophammers that drive piles to required depths.</t>
+  </si>
+  <si>
+    <t>47-2073.00</t>
+  </si>
+  <si>
+    <t>Operating Engineers and Other Construction Equipment Operators</t>
+  </si>
+  <si>
+    <t>Back Hoe Operator | Engineering Equipment Operator | Equipment Operator (EO) | Forklift Operator | Heavy Equipment Operator (HEO) | Hot Mix Asphalt Operator | Machine Operator | Motor Grader Operator | Operating Engineer | Track Hoe Operator</t>
+  </si>
+  <si>
+    <t>Maintenance record software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Work record software</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Control Precision | Depth Perception | Multilimb Coordination | Near Vision | Far Vision | Rate Control | Reaction Time | Arm-Hand Steadiness | Response Orientation | Problem Sensitivity | Oral Comprehension | Visualization | Perceptual Speed | Manual Dexterity | Speech Clarity | Speech Recognition | Auditory Attention | Hearing Sensitivity | Visual Color Discrimination | Static Strength | Finger Dexterity | Time Sharing | Selective Attention | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Consequence of Error | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Exposed to Hazardous Equipment | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Work Outcomes and Results of Other Workers | In an Open Vehicle or Operating Equipment | Health and Safety of Other Workers | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Telephone Conversations | Work With or Contribute to a Work Group or Team | Time Pressure | In an Enclosed Vehicle or Operate Enclosed Equipment | Freedom to Make Decisions | Pace Determined by Speed of Equipment | Exposed to Whole Body Vibration | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Physical Proximity | Exposed to Very Hot or Cold Temperatures | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Continuous Mining Machine Operators | Crane and Tower Operators | Dredge Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Extraction Workers | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Rail-Track Laying and Maintenance Equipment Operators | Riggers</t>
+  </si>
+  <si>
+    <t>Operate one or several types of power construction equipment, such as motor graders, bulldozers, scrapers, compressors, pumps, derricks, shovels, tractors, or front-end loaders to excavate, move, and grade earth, erect structures, or pour concrete or other hard surface pavement. May repair and maintain equipment in addition to other duties.</t>
+  </si>
+  <si>
+    <t>Adjust handwheels and depress pedals to control attachments, such as blades, buckets, scrapers, or swing booms. | Align machines, cutterheads, or depth gauge makers with reference stakes and guidelines or ground or position equipment, following hand signals of other workers. | Check fuel supplies at sites to ensure adequate availability. | Connect hydraulic hoses, belts, mechanical linkages, or power takeoff shafts to tractors. | Coordinate machine actions with other activities, positioning or moving loads in response to hand or audio signals from crew members. | Drive and maneuver equipment equipped with blades in successive passes over working areas to remove topsoil, vegetation, or rocks or to distribute and level earth or terrain. | Drive tractor-trailer trucks to move equipment from site to site. | Keep records of material or equipment usage or problems encountered. | Learn and follow safety regulations. | Load and move dirt, rocks, equipment, or other materials, using trucks, crawler tractors, power cranes, shovels, graders, or related equipment. | Locate underground services, such as pipes or wires, prior to beginning work. | Monitor operations to ensure that health and safety standards are met. | Operate compactors, scrapers, or rollers to level, compact, or cover refuse at disposal grounds. | Operate equipment to demolish or remove debris or to remove snow from streets, roads, or parking lots. | Operate loaders to pull out stumps, rip asphalt or concrete, rough-grade properties, bury refuse, or perform general cleanup. | Operate road watering, oiling, or rolling equipment, or street sealing equipment, such as chip spreaders. | Operate tractors or bulldozers to perform such tasks as clearing land, mixing sludge, trimming backfills, or building roadways or parking lots. | Push other equipment when extra traction or assistance is required. | Repair and maintain equipment, making emergency adjustments or assisting with major repairs as necessary. | Select and fasten bulldozer blades or other attachments to tractors, using hitches. | Signal operators to guide movement of tractor-drawn machines. | Start engines, move throttles, switches, or levers, or depress pedals to operate machines, such as bulldozers, trench excavators, road graders, or backhoes. | Take actions to avoid potential hazards or obstructions, such as utility lines, other equipment, other workers, or falling objects. | Talk to clients and study instructions, plans, or diagrams to establish work requirements. | Test atmosphere for adequate oxygen or explosive conditions when working in confined spaces. | Turn valves to control air or water output of compressors or pumps.</t>
+  </si>
+  <si>
+    <t>47-2081.00</t>
+  </si>
+  <si>
+    <t>Drywall and Ceiling Tile Installers</t>
+  </si>
+  <si>
+    <t>Ceiling Installer | Dry Wall Installer | Drywall Finisher | Drywall Hanger | Drywall Installer | Drywall Mechanic | Drywaller | Exterior Interior Specialist | Metal Framer | Metal Stud Framer</t>
+  </si>
+  <si>
+    <t>Business management software | Construction Software Center EasyEst | DevWave Estimate Works | Job costing software | Logic Group Scanner Digitizing Software | Microsoft Office software | Microsoft Windows | Microsoft Word | On Center Quick Bid | Turtle Creek Software Goldenseal | Wilhelm Publishing Threshold</t>
+  </si>
+  <si>
+    <t>Critical Thinking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mathematics | Mechanical | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Trunk Strength | Extent Flexibility | Near Vision | Gross Body Equilibrium | Finger Dexterity | Static Strength | Visualization | Oral Expression | Oral Comprehension | Stamina | Multilimb Coordination | Control Precision | Selective Attention | Information Ordering | Speech Recognition | Far Vision | Perceptual Speed | Deductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Telephone Conversations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Freedom to Make Decisions | Spend Time Walking or Running | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Time Pressure | Contact With Others | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Construction Laborers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Plasterers and Stucco Masons | Reinforcing Iron and Rebar Workers | Roofers | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Tapers | Terrazzo Workers and Finishers | Tile and Stone Setters | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Apply plasterboard or other wallboard to ceilings or interior walls of buildings. Apply or mount acoustical tiles or blocks, strips, or sheets of shock-absorbing materials to ceilings and walls of buildings to reduce or reflect sound. Materials may be of decorative quality. Includes lathers who fasten wooden, metal, or rockboard lath to walls, ceilings, or partitions of buildings to provide support base for plaster, fireproofing, or acoustical material.</t>
+  </si>
+  <si>
+    <t>Apply cement to backs of tiles and press tiles into place, aligning them with layout marks or joints of previously laid tile. | Apply or mount acoustical tile or blocks, strips, or sheets of shock-absorbing materials to ceilings or walls of buildings to reduce reflection of sound or to decorate rooms. | Assemble or install metal framing or decorative trim for windows, doorways, or vents. | Coordinate work with drywall finishers who cover the seams between drywall panels. | Cut and screw together metal channels to make floor or ceiling frames, according to plans for the location of rooms or hallways. | Cut fixture or border tiles to size, using keyhole saws, and insert them into surrounding frameworks. | Cut metal or wood framing and trim to size, using cutting tools. | Fasten metal or rockboard lath to the structural framework of walls, ceilings, or partitions of buildings, using nails, screws, staples, or wire-ties. | Fit and fasten wallboard or drywall into position on wood or metal frameworks, using glue, nails, or screws. | Hang dry lines to wall moldings to guide positioning of main runners. | Hang drywall panels on metal frameworks of walls and ceilings in offices, schools, or other large buildings, using lifts or hoists to adjust panel heights, when necessary. | Inspect furrings, mechanical mountings, or masonry surfaces for plumbness and level, using spirit or water levels. | Install blanket insulation between studs and tack plastic moisture barriers over insulation. | Install horizontal and vertical metal or wooden studs to frames so that wallboard can be attached to interior walls. | Install metal lath where plaster applications will be exposed to weather or water, or for curved or irregular surfaces. | Measure and cut openings in panels or tiles for electrical outlets, windows, vents, plumbing, or other fixtures, using keyhole saws or other cutting tools. | Measure and mark surfaces to lay out work, according to blueprints or drawings, using tape measures, straightedges or squares, and marking devices. | Mount tile, using adhesives, or by nailing, screwing, stapling, or wire-tying lath directly to structural frameworks. | Nail channels or wood furring strips to surfaces to provide mounting for tile. | Read blueprints or other specifications to determine methods of installation, work procedures, or material or tool requirements. | Remove existing plaster, drywall, or paneling, using crowbars and hammers. | Scribe and cut edges of tile to fit walls where wall molding is not specified. | Seal joints between ceiling tiles and walls. | Suspend angle iron grids or channel irons from ceilings, using wire. | Trim rough edges from wallboard to maintain even joints, using knives. | Wash concrete surfaces before mounting tile to increase adhesive qualities of surfaces, using washing soda and zinc sulfate solution.</t>
+  </si>
+  <si>
+    <t>47-2082.00</t>
+  </si>
+  <si>
+    <t>Tapers</t>
+  </si>
+  <si>
+    <t>Drywall Finisher | Drywall Mechanic | Drywall Taper | Finisher | Taper</t>
+  </si>
+  <si>
+    <t>Applied Computer Systems JOBPOWER | Construction Software Center EasyEst | DevWave Estimate Works | Intuit QuickBooks | Microsoft Dynamics | Microsoft Office software | On Center Quick Bid | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Building and Construction</t>
+  </si>
+  <si>
+    <t>Near Vision | Extent Flexibility | Trunk Strength | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Exposed to Contaminants | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure | Work With or Contribute to a Work Group or Team | Spend Time Walking or Running | Health and Safety of Other Workers | Exposed to High Places | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Telephone Conversations | Indoors, Not Environmentally Controlled | Spend Time Bending or Twisting Your Body | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Grinding and Polishing Workers, Hand | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Painters, Construction and Maintenance | Plasterers and Stucco Masons | Reinforcing Iron and Rebar Workers | Roofers | Sheet Metal Workers | Structural Iron and Steel Workers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Seal joints between plasterboard or other wallboard to prepare wall surface for painting or papering.</t>
+  </si>
+  <si>
+    <t>Apply additional coats to fill in holes and make surfaces smooth. | Apply texturizing compounds or primers to walls or ceilings before final finishing, using trowels, brushes, rollers, or spray guns. | Check adhesives to ensure that they will work and will remain durable. | Countersink nails or screws below surfaces of walls before applying sealing compounds, using hammers or screwdrivers. | Install metal molding at wall corners to secure wallboard. | Mix sealing compounds by hand or with portable electric mixers. | Press paper tape over joints to embed tape into sealing compound and to seal joints. | Remove extra compound after surfaces have been covered sufficiently. | Sand or patch nicks or cracks in plasterboard or wallboard. | Sand rough spots of dried cement between applications of compounds. | Seal joints between plasterboard or other wallboard to prepare wall surfaces for painting or papering. | Select the correct sealing compound or tape. | Spread and smooth cementing material over tape, using trowels or floating machines to blend joints with wall surfaces. | Spread sealing compound between boards or panels or over cracks, holes, nail heads, or screw heads, using trowels, broadknives, or spatulas. | Use mechanical applicators that spread compounds and embed tape in one operation. | Work on high ceilings, using scaffolding or other tools, such as stilts.</t>
+  </si>
+  <si>
+    <t>47-2111.00</t>
+  </si>
+  <si>
+    <t>Electricians</t>
+  </si>
+  <si>
+    <t>Control Electrician | Electrical Journey Person | Electrical Troubleshooter | Electrician | Housing Maintenance Electrician | Industrial Electrician | Inside Wireman | Maintenance Electrician | Paper Mill Electrician | Wireman</t>
+  </si>
+  <si>
+    <t>AVEVA InTouch HMI | Adobe Acrobat | Autodesk AutoCAD | Construction Master Pro | Craftsman CD Estimator | Database software | Electrosoft FlashWorks | Elite Software E-Coord | Elite Software Inpoint | Elite Software Outpoint | Elite Software Short | Elite Software VDROP | Insight Direct ServiceCEO | Lighting calculation software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | One Mile Up Panel Planner | Programmable logic controller PLC software | Resolve Systems Service Management | SAP software | Sage 300 Construction and Real Estate | Shafer Service Systems | SmartDraw | Socrates Contractor's Library | SoftEmpire Electrical Calculations | Supervisory control and data acquisition SCADA software | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Active Learning | Reading Comprehension | Monitoring | Learning Strategies | Mathematics | Writing</t>
+  </si>
+  <si>
+    <t>Building and Construction | Administration and Management | Mechanical | Mathematics | Design | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Deductive Reasoning | Inductive Reasoning | Information Ordering | Finger Dexterity | Oral Comprehension | Arm-Hand Steadiness | Visual Color Discrimination | Extent Flexibility | Trunk Strength | Visualization | Oral Expression | Written Comprehension | Category Flexibility | Flexibility of Closure | Manual Dexterity | Far Vision | Control Precision | Selective Attention | Mathematical Reasoning | Speech Clarity | Speech Recognition | Depth Perception | Gross Body Equilibrium | Multilimb Coordination | Perceptual Speed | Number Facility | Fluency of Ideas | Written Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Impact of Decisions on Co-workers or Company Results | Exposed to Hazardous Conditions | Spend Time Standing | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Telephone Conversations | Exposed to Contaminants | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Cramped Work Space, Awkward Positions | Work Outcomes and Results of Other Workers | Spend Time Making Repetitive Motions | Time Pressure | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Walking or Running | Indoors, Not Environmentally Controlled | Determine Tasks, Priorities and Goals | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to Very Hot or Cold Temperatures | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | E-Mail | Spend Time Keeping or Regaining Balance | Deal With External Customers or the Public in General | Outdoors, Under Cover | Spend Time Kneeling, Crouching, Stooping, or Crawling | Exposed to Extremely Bright or Inadequate Lighting Conditions | Exposed to High Places | In an Enclosed Vehicle or Operate Enclosed Equipment</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Carpenters | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Mechanical | Lighting Technicians | Maintenance and Repair Workers, General | Millwrights | Plumbers, Pipefitters, and Steamfitters | Sheet Metal Workers | Solar Photovoltaic Installers | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Install, maintain, and repair electrical wiring, equipment, and fixtures. Ensure that work is in accordance with relevant codes. May install or service street lights, intercom systems, or electrical control systems.</t>
+  </si>
+  <si>
+    <t>Advise management on whether continued operation of equipment could be hazardous. | Assemble, install, test, or maintain electrical or electronic wiring, equipment, appliances, apparatus, or fixtures, using hand tools or power tools. | Connect wires to circuit breakers, transformers, or other components. | Construct or fabricate parts, using hand tools, according to specifications. | Diagnose malfunctioning systems, apparatus, or components, using test equipment and hand tools to locate the cause of a breakdown and correct the problem. | Direct or train workers to install, maintain, or repair electrical wiring, equipment, or fixtures. | Fasten small metal or plastic boxes to walls to house electrical switches or outlets. | Inspect electrical systems, equipment, or components to identify hazards, defects, or the need for adjustment or repair, and to ensure compliance with codes. | Install ground leads and connect power cables to equipment, such as motors. | Maintain current electrician's license or identification card to meet governmental regulations. | Perform business management duties, such as maintaining records or files, preparing reports, or ordering supplies or equipment. | Perform physically demanding tasks, such as digging trenches to lay conduit or moving or lifting heavy objects. | Place conduit, pipes, or tubing, inside designated partitions, walls, or other concealed areas, and pull insulated wires or cables through the conduit to complete circuits between boxes. | Plan layout and installation of electrical wiring, equipment, or fixtures, based on job specifications and local codes. | Prepare sketches or follow blueprints to determine the location of wiring or equipment and to ensure conformance to building and safety codes. | Provide assistance during emergencies by operating floodlights or generators, placing flares, or driving needed vehicles. | Provide preliminary sketches or cost estimates for materials or services. | Repair or replace wiring, equipment, or fixtures, using hand tools or power tools. | Test electrical systems or continuity of circuits in electrical wiring, equipment, or fixtures, using testing devices, such as ohmmeters, voltmeters, or oscilloscopes, to ensure compatibility and safety of system. | Use a variety of tools or equipment, such as power construction equipment, measuring devices, power tools, and testing equipment, such as oscilloscopes, ammeters, or test lamps. | Work from ladders, scaffolds, or roofs to install, maintain, or repair electrical wiring, equipment, or fixtures.</t>
+  </si>
+  <si>
+    <t>47-2121.00</t>
+  </si>
+  <si>
+    <t>Glaziers</t>
+  </si>
+  <si>
+    <t>Auto Glass Tech (Automobile Glass Technician) | Commercial Glazier | Field Glazier | Glass Installer | Glass Technician (Glass Tech) | Glassman | Glazer | Glazier | Glazier Worker | Union Glazier</t>
+  </si>
+  <si>
+    <t>American Glazing Software AGS WindowPricer | BidMaster | D-CALC FACADE 4000 | Microsoft Excel | Microsoft Office software | Microsoft Windows | Work order software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Mathematics | Administration and Management | Design | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Trunk Strength | Multilimb Coordination | Manual Dexterity | Problem Sensitivity | Information Ordering | Static Strength | Control Precision | Speech Clarity | Speech Recognition | Far Vision | Gross Body Equilibrium | Extent Flexibility | Finger Dexterity | Selective Attention | Visualization | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Written Comprehension | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Importance of Being Exact or Accurate | Contact With Others | Work With or Contribute to a Work Group or Team | Spend Time Standing | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Freedom to Make Decisions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work Outcomes and Results of Other Workers | Time Pressure | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Indoors, Not Environmentally Controlled | Consequence of Error | Outdoors, Under Cover | Exposed to High Places | Telephone Conversations | Spend Time Bending or Twisting Your Body | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Automotive Glass Installers and Repairers | Brickmasons and Blockmasons | Cabinetmakers and Bench Carpenters | Carpenters | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Furniture Finishers | Glass Blowers, Molders, Benders, and Finishers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Mechanical Door Repairers | Molders, Shapers, and Casters, Except Metal and Plastic | Plasterers and Stucco Masons | Roofers | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Install glass in windows, skylights, store fronts, and display cases, or on surfaces, such as building fronts, interior walls, ceilings, and tabletops.</t>
+  </si>
+  <si>
+    <t>Assemble and cement sections of stained glass together. | Assemble, erect, or dismantle scaffolds, rigging, or hoisting equipment. | Confer with customers to determine project requirements or to provide cost estimates. | Create patterns on glass by etching, sandblasting, or painting designs. | Cut and attach mounting strips, metal or wood moldings, rubber gaskets, or metal clips to surfaces in preparation for mirror installation. | Cut and remove broken glass prior to installing replacement glass. | Cut, assemble, fit, or attach metal-framed glass enclosures for showers, bathtubs, display cases, skylights, solariums, or other structures. | Cut, fit, install, repair, or replace glass or glass substitutes, such as plastic or aluminum, in building interiors or exteriors or in furniture or other products. | Determine plumb of walls or ceilings, using plumb lines and levels. | Drive trucks to installation sites and unload mirrors, glass equipment, or tools. | Fabricate or install metal sashes or moldings for glass installation, using aluminum or steel framing. | Fasten glass panes into wood sashes or frames with clips, points, or moldings, adding weather seals or putty around pane edges to seal joints. | Grind or polish glass, smoothing edges when necessary. | Install pre-assembled metal or wood frameworks for windows or doors to be fitted with glass panels, using hand tools. | Load and arrange glass or mirrors onto delivery trucks, using suction cups or cranes to lift glass. | Measure and mark outlines or patterns on glass to indicate cutting lines. | Measure mirrors and dimensions of areas to be covered to determine work procedures. | Measure, cut, fit, and press anti-glare adhesive film to glass or spray glass with tinting solution to prevent light glare. | Move furniture to clear work sites and cover floors or furnishings with drop cloths. | Operate cranes or hoists with suction cups to lift large, heavy pieces of glass. | Pack spaces between moldings and glass with glazing compounds and trim excess material with glazing knives. | Prepare glass for cutting by resting it on rack edges or against cutting tables and brushing thin layer of oil along cutting lines or dipping cutting tools in oil. | Read and interpret blueprints or specifications to determine size, shape, color, type, or thickness of glass, location of framing, installation procedures, or staging or scaffolding materials required. | Score glass with cutters' wheels, breaking off excess glass by hand or with notched tools. | Secure mirrors in position, using mastic cement, putty, bolts, or screws. | Select the type or color of glass or mirror according to specifications. | Set glass doors into frames and bolt metal hinges, handles, locks, or other hardware to attach doors to frames and walls.</t>
+  </si>
+  <si>
+    <t>47-2131.00</t>
+  </si>
+  <si>
+    <t>Insulation Workers, Floor, Ceiling, and Wall</t>
+  </si>
+  <si>
+    <t>Attic Blower | Insulation Estimator | Insulation Installer | Insulation Mechanic | Insulation Worker | Insulator | Retrofit Installer | Spray Foam Installer | Warehouse Insulation Worker</t>
+  </si>
+  <si>
+    <t>CMSN FieldPAK | Comput-Ability Mechanical Insulation Key Estimator | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | North American Insulation Manufacturers Association NAIMA 3E Plus | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | Mechanical</t>
+  </si>
+  <si>
+    <t>Extent Flexibility | Multilimb Coordination | Manual Dexterity | Gross Body Equilibrium | Trunk Strength | Arm-Hand Steadiness | Control Precision | Visualization | Speech Clarity | Depth Perception | Near Vision | Stamina | Static Strength | Finger Dexterity | Selective Attention | Oral Expression</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Time Pressure | Exposed to Very Hot or Cold Temperatures | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Outdoors, Exposed to All Weather Conditions | Indoors, Not Environmentally Controlled | Spend Time Making Repetitive Motions | Exposed to Cramped Work Space, Awkward Positions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Exposed to High Places | In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making | Telephone Conversations | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Fiberglass Laminators and Fabricators | Floor Layers, Except Carpet, Wood, and Hard Tiles | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Pipelayers | Plasterers and Stucco Masons | Plumbers, Pipefitters, and Steamfitters | Roofers | Sheet Metal Workers | Solar Thermal Installers and Technicians | Tapers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Line and cover structures with insulating materials. May work with batt, roll, or blown insulation materials.</t>
+  </si>
+  <si>
+    <t>Cover and line structures with blown or rolled forms of materials to insulate against cold, heat, or moisture, using saws, knives, rasps, trowels, blowers, or other tools and implements. | Cover, seal, or finish insulated surfaces or access holes with plastic covers, canvas strips, sealants, tape, cement or asphalt mastic. | Distribute insulating materials evenly into small spaces within floors, ceilings, or walls, using blowers and hose attachments, or cement mortars. | Fill blower hoppers with insulating materials. | Fit, wrap, staple, or glue insulating materials to structures or surfaces, using hand tools or wires. | Measure and cut insulation for covering surfaces, using tape measures, handsaws, power saws, knives, or scissors. | Move controls, buttons, or levers to start blowers and regulate flow of materials through nozzles. | Prepare surfaces for insulation application by brushing or spreading on adhesives, cement, or asphalt, or by attaching metal pins to surfaces. | Read blueprints, and select appropriate insulation, based on space characteristics and the heat retaining or excluding characteristics of the material. | Remove old insulation, such as asbestos, following safety procedures.</t>
+  </si>
+  <si>
+    <t>47-2132.00</t>
+  </si>
+  <si>
+    <t>Insulation Workers, Mechanical</t>
+  </si>
+  <si>
+    <t>Commercial Insulator | Heat and Frost Insulator | Industrial Insulator | Insulation Installer | Insulation Mechanic | Insulation Worker | Insulator | Insulator Journeyman | Mechanic Insulator | Mechanical Insulator</t>
+  </si>
+  <si>
+    <t>CMSN FieldPAK | Comput-Ability Mechanical Insulation Key Estimator | IBM Maximo Asset Management | North American Insulation Manufacturers Association NAIMA 3E Plus | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | Mechanical | Administration and Management | Education and Training | Mathematics | Public Safety and Security | Production and Processing | English Language | Design | Sales and Marketing | Personnel and Human Resources | Transportation</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Extent Flexibility | Problem Sensitivity | Information Ordering | Oral Expression | Oral Comprehension | Near Vision | Gross Body Equilibrium | Static Strength | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Gross Body Coordination | Finger Dexterity | Category Flexibility | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Climbing Ladders, Scaffolds, or Poles | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Telephone Conversations | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Exposed to Cramped Work Space, Awkward Positions | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Indoors, Not Environmentally Controlled | Health and Safety of Other Workers | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Exposed to High Places | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Physical Proximity | Work Outcomes and Results of Other Workers | Exposed to Very Hot or Cold Temperatures | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Brickmasons and Blockmasons | Carpet Installers | Drywall and Ceiling Tile Installers | Fiberglass Laminators and Fabricators | Floor Layers, Except Carpet, Wood, and Hard Tiles | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Molders, Shapers, and Casters, Except Metal and Plastic | Pipelayers | Plasterers and Stucco Masons | Plumbers, Pipefitters, and Steamfitters | Roofers | Sheet Metal Workers | Solar Thermal Installers and Technicians | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Tapers | Tile and Stone Setters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Apply insulating materials to pipes or ductwork, or other mechanical systems in order to help control and maintain temperature.</t>
+  </si>
+  <si>
+    <t>Apply, remove, and repair insulation on industrial equipment, pipes, ductwork, or other mechanical systems such as heat exchangers, tanks, and vessels, to help control noise and maintain temperatures. | Cover, seal, or finish insulated surfaces or access holes with plastic covers, canvas strips, sealants, tape, cement, or asphalt mastic. | Determine the amounts and types of insulation needed, and methods of installation, based on factors such as location, surface shape, and equipment use. | Fit insulation around obstructions, and shape insulating materials and protective coverings as required. | Install sheet metal around insulated pipes with screws to protect the insulation from weather conditions or physical damage. | Measure and cut insulation for covering surfaces, using tape measures, handsaws, knives, and scissors. | Prepare surfaces for insulation application by brushing or spreading on adhesives, cement, or asphalt, or by attaching metal pins to surfaces. | Read blueprints and specifications to determine job requirements. | Select appropriate insulation, such as fiberglass, Styrofoam, or cork, based on the heat retaining or excluding characteristics of the material.</t>
+  </si>
+  <si>
+    <t>47-2141.00</t>
+  </si>
+  <si>
+    <t>Painters, Construction and Maintenance</t>
+  </si>
+  <si>
+    <t>Building Trades Painter | Commercial Painter | Facilities Painter | Highway Painter | House Painter | Industrial Painter | Maintenance Painter | Painter | Professional Painter | Texturer</t>
+  </si>
+  <si>
+    <t>Act! | Corel Paint Shop Pro | Corel Painter | Evergreen Technology Eagle Bid Estimating | Evergreen Technology Total Faux | Insight Direct ServiceCEO | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | On Center Quick Bid | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Building and Construction</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Manual Dexterity | Trunk Strength | Speech Clarity | Visual Color Discrimination | Gross Body Equilibrium | Gross Body Coordination | Extent Flexibility | Multilimb Coordination | Deductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Importance of Being Exact or Accurate | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to Contaminants | Exposed to High Places | Health and Safety of Other Workers | Deal With External Customers or the Public in General | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Spend Time Walking or Running | Spend Time Bending or Twisting Your Body | Physical Proximity | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Written Letters and Memos | Spend Time Kneeling, Crouching, Stooping, or Crawling</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Furniture Finishers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Paperhangers | Plasterers and Stucco Masons | Roofers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Paint walls, equipment, buildings, bridges, and other structural surfaces, using brushes, rollers, and spray guns. May remove old paint to prepare surface prior to painting. May mix colors or oils to obtain desired color or consistency.</t>
+  </si>
+  <si>
+    <t>Apply paint, stain, varnish, enamel, or other finishes to equipment, buildings, bridges, or other structures, using brushes, spray guns, or rollers. | Apply primers or sealers to prepare new surfaces, such as bare wood or metal, for finish coats. | Calculate amounts of required materials and estimate costs, based on surface measurements or work orders. | Cover surfaces with dropcloths or masking tape and paper to protect surfaces during painting. | Cut stencils and brush or spray lettering or decorations on surfaces. | Erect scaffolding or swing gates, or set up ladders, to work above ground level. | Fill cracks, holes, or joints with caulk, putty, plaster, or other fillers, using caulking guns or putty knives. | Mix and match colors of paint, stain, or varnish with oil or thinning and drying additives to obtain desired colors and consistencies. | Polish final coats to specified finishes. | Read work orders or receive instructions from supervisors or homeowners to determine work requirements. | Remove fixtures such as pictures, door knobs, lamps, or electric switch covers prior to painting. | Remove old finishes by stripping, sanding, wire brushing, burning, or using water or abrasive blasting. | Select and purchase tools or finishes for surfaces to be covered, considering durability, ease of handling, methods of application, and customers' wishes. | Smooth surfaces, using sandpaper, scrapers, brushes, steel wool, or sanding machines. | Use special finishing techniques such as sponging, ragging, layering, or faux finishing. | Wash and treat surfaces with oil, turpentine, mildew remover, or other preparations, and sand rough spots to ensure that finishes will adhere properly. | Waterproof buildings, using waterproofers or caulking.</t>
+  </si>
+  <si>
+    <t>47-2142.00</t>
+  </si>
+  <si>
+    <t>Paperhangers</t>
+  </si>
+  <si>
+    <t>Bill Board Poster | Bill Poster | Hanger | Paper Hanger | Paperhanger | Vinyl Hanger | Wall Covering Contractor | Wall Covering Installer | Wallpaper Hanger | Wallpaper Installer</t>
+  </si>
+  <si>
+    <t>A-Systems JobView | Construction Software Center EasyEst | Corel Painter | Electronic data interchange EDI software | Google Docs | Microsoft Excel | Microsoft Word | On Center Quick Bid | PlanSwift | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Building and Construction | Mathematics | Mechanical | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Arm-Hand Steadiness | Extent Flexibility | Multilimb Coordination | Gross Body Equilibrium | Finger Dexterity | Trunk Strength | Control Precision | Information Ordering | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Spend Time Climbing Ladders, Scaffolds, or Poles | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Time Pressure | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Carpenters | Carpet Installers | Drywall and Ceiling Tile Installers | Fiberglass Laminators and Fabricators | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Furniture Finishers | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Layout Workers, Metal and Plastic | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Plasterers and Stucco Masons | Roofers | Sheet Metal Workers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Cover interior walls or ceilings of rooms with decorative wallpaper or fabric, or attach advertising posters on surfaces such as walls and billboards. May remove old materials or prepare surfaces to be papered.</t>
+  </si>
+  <si>
+    <t>Apply acetic acid to damp plaster to prevent lime from bleeding through paper. | Apply adhesives to the backs of paper strips, using brushes, or dunk strips of prepasted wallcovering in water, wiping off any excess adhesive. | Apply sizing to seal surfaces and maximize adhesion of coverings to surfaces. | Apply thinned glue to waterproof porous surfaces, using brushes, rollers, or pasting machines. | Check finished wallcoverings for proper alignment, pattern matching, and neatness of seams. | Cover interior walls and ceilings of rooms with decorative wallpaper or fabric, using hand tools. | Fill holes, cracks, and other surface imperfections preparatory to covering surfaces. | Mark vertical guidelines on walls to align strips, using plumb bobs and chalk lines. | Measure and cut strips from rolls of wallpaper or fabric, using shears or razors. | Measure surfaces or review work orders to estimate the quantities of materials needed. | Mix paste, using paste powder and water, and brush paste onto surfaces. | Place strips or sections of paper on surfaces, aligning section edges and patterns. | Remove old paper, using water, steam machines, or solvents and scrapers. | Remove paint, varnish, dirt, and grease from surfaces, using paint remover and water soda solutions. | Set up equipment, such as pasteboards and scaffolds. | Smooth rough spots on walls and ceilings, using sandpaper. | Smooth strips or sections of paper with brushes or rollers to remove wrinkles and bubbles and to smooth joints. | Staple or tack advertising posters onto fences, walls, billboards, or poles. | Trim excess material at ceilings or baseboards, using knives. | Trim rough edges from strips, using straightedges and trimming knives.</t>
+  </si>
+  <si>
+    <t>47-2151.00</t>
+  </si>
+  <si>
+    <t>Pipelayers</t>
+  </si>
+  <si>
+    <t>Pipelayer | Tailman</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Building and Construction | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Control Precision | Arm-Hand Steadiness | Oral Comprehension | Static Strength | Speech Clarity | Speech Recognition | Depth Perception | Near Vision | Problem Sensitivity | Oral Expression | Extent Flexibility | Stamina | Trunk Strength | Reaction Time | Rate Control | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Selective Attention | Visualization | Information Ordering</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Work With or Contribute to a Work Group or Team | Contact With Others | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Exposed to Very Hot or Cold Temperatures | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Control and Valve Installers and Repairers, Except Mechanical Door | Drywall and Ceiling Tile Installers | Electrical Power-Line Installers and Repairers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Paving, Surfacing, and Tamping Equipment Operators | Plumbers, Pipefitters, and Steamfitters | Reinforcing Iron and Rebar Workers | Rotary Drill Operators, Oil and Gas | Septic Tank Servicers and Sewer Pipe Cleaners | Sheet Metal Workers | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Lay pipe for storm or sanitation sewers, drains, and water mains. Perform any combination of the following tasks: grade trenches or culverts, position pipe, or seal joints.</t>
+  </si>
+  <si>
+    <t>Align and position pipes to prepare them for welding or sealing. | Check slopes for conformance to requirements, using levels or lasers. | Connect pipe pieces and seal joints, using welding equipment, cement, or glue. | Cover pipes with earth or other materials. | Cut pipes to required lengths. | Dig trenches to desired or required depths, by hand or using trenching tools. | Grade or level trench bases, using tamping machines or hand tools. | Install or repair sanitary or stormwater sewer structures or pipe systems. | Install or use instruments such as lasers, grade rods, or transit levels. | Lay out pipe routes, following written instructions or blueprints and coordinating layouts with supervisors. | Locate existing pipes needing repair or replacement, using magnetic or radio indicators. | Operate mechanized equipment, such as pickup trucks, rollers, tandem dump trucks, front-end loaders, or backhoes. | Tap and drill holes into pipes to introduce auxiliary lines or devices. | Train or supervise others in laying pipe.</t>
+  </si>
+  <si>
+    <t>47-2152.00</t>
+  </si>
+  <si>
+    <t>Plumbers, Pipefitters, and Steamfitters</t>
+  </si>
+  <si>
+    <t>Drain Technician | Fire Sprinkler Service Technician | Pipe Welder | Pipefitter | Plumber | Plumbing Installer | Residential Plumber | Service Plumber | Sprinkler Fitter | Steamfitter</t>
+  </si>
+  <si>
+    <t>AEC Design Group CADPIPE | Atlas Construction Business Forms | Autodesk Building Systems | Bentley Systems AutoPIPE | Bookkeeping software | COADE CAESAR II | Database software | Drawing and drafting software | Elite Software DPIPE | Elite Software FIRE | Elite Software HSYM | Elite Software Plumbing CAD | Elite Software Spipe | Elite Software Sprinkler CAD | Email software | Estimating software | FastEST FastPipe | FastEST software | Heat loss calculation software | Horizon Engineering Sigma Plumbing Calculator | Insight Direct ServiceCEO | Intuit QuickBooks | Job costing software | KRS Enterprises Service First! | Klear Estimator | Maintenance management software | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Word | Pipepro Pipefitting | Piping construction costs estimation software | PipingOffice | PricePoint | Quicken | Quote Software QuoteExpress | Vision InfoSoft Plumbing Bid Manager | ViziFlow | Watter Hammer Software Hytran | Wilhelm Publishing Threshold | Wintac Pro</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Design | Mathematics | Customer and Personal Service | Administration and Management | Engineering and Technology | Public Safety and Security | Physics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Finger Dexterity | Near Vision | Manual Dexterity | Deductive Reasoning | Inductive Reasoning | Far Vision | Trunk Strength | Category Flexibility | Visualization | Arm-Hand Steadiness | Oral Comprehension | Oral Expression | Multilimb Coordination | Control Precision | Selective Attention | Information Ordering | Extent Flexibility | Dynamic Strength | Static Strength | Perceptual Speed | Flexibility of Closure | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Time Pressure | Indoors, Not Environmentally Controlled | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Contact With Others | Telephone Conversations | Determine Tasks, Priorities and Goals | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Spend Time Walking or Running | Physical Proximity | Spend Time Bending or Twisting Your Body | Exposed to Cramped Work Space, Awkward Positions | Exposed to High Places | Work Outcomes and Results of Other Workers | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to Minor Burns, Cuts, Bites, or Stings | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Very Hot or Cold Temperatures | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Carpenters | Construction Laborers | Control and Valve Installers and Repairers, Except Mechanical Door | Electricians | Engine and Other Machine Assemblers | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Maintenance and Repair Workers, General | Millwrights | Pipelayers | Septic Tank Servicers and Sewer Pipe Cleaners | Sheet Metal Workers | Solar Thermal Installers and Technicians | Stationary Engineers and Boiler Operators | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Assemble, install, alter, and repair pipelines or pipe systems that carry water, steam, air, or other liquids or gases. May install heating and cooling equipment and mechanical control systems. Includes sprinkler fitters.</t>
+  </si>
+  <si>
+    <t>Anchor steel supports from ceiling joists to hold pipes in place. | Assemble pipe sections, tubing, or fittings, using couplings, clamps, screws, bolts, cement, plastic solvent, caulking, or soldering, brazing, or welding equipment. | Attach pipes to walls, structures, or fixtures, such as radiators or tanks, using brackets, clamps, tools, or welding equipment. | Cut openings in structures to accommodate pipes or pipe fittings, using hand or power tools. | Cut, thread, or hammer pipes to specifications, using tools such as saws, cutting torches, pipe threaders, or pipe benders. | Direct helpers engaged in pipe cutting, preassembly, or installation of plumbing systems or components. | Estimate time, material, or labor costs for use in project plans. | Fill pipes or plumbing fixtures with water or air and observe pressure gauges to detect and locate leaks. | Inspect structures to assess material or equipment needs, to establish the sequence of pipe installations, or to plan installation around obstructions, such as electrical wiring. | Inspect work sites for obstructions or holes that could cause structural weakness. | Inspect, examine, or test installed systems or pipe lines, using pressure gauge, hydrostatic testing, observation, or other methods. | Install automatic controls to regulate pipe systems. | Install fixtures, appliances, or equipment designed to reduce water or energy consumption. | Install green plumbing equipment, such as faucet flow restrictors, dual-flush or pressure-assisted flush toilets, or tankless hot water heaters. | Install pipe assemblies, fittings, valves, appliances such as dishwashers or water heaters, or fixtures such as sinks or toilets, using hand or power tools. | Install pipe systems to support alternative energy-fueled systems, such as geothermal heating or cooling systems. | Install underground storm, sanitary, or water piping systems, extending piping as needed to connect fixtures and plumbing. | Keep records of work assignments. | Lay out full scale drawings of pipe systems, supports, or related equipment, according to blueprints. | Locate and mark the position of pipe installations, connections, passage holes, or fixtures in structures, using measuring instruments such as rulers or levels. | Maintain or repair plumbing by replacing defective washers, replacing or mending broken pipes, or opening clogged drains. | Modify, clean, or maintain pipe systems, units, fittings, or related machines or equipment, using hand or power tools. | Operate motorized pumps to remove water from flooded manholes, basements, or facility floors. | Plan pipe system layout, installation, or repair, according to specifications. | Repair hydraulic or air pumps. | Repair or remove and replace system components. | Review blueprints, building codes, or specifications to determine work details or procedures. | Select pipe sizes, types, or related materials, such as supports, hangers, or hydraulic cylinders, according to specifications. | Shut off steam, water, or other gases or liquids from pipe sections, using valve keys or wrenches. | Weld small pipes or special piping, using specialized techniques, equipment, or materials, such as computer-assisted welding or microchip fabrication.</t>
+  </si>
+  <si>
+    <t>47-2152.04</t>
+  </si>
+  <si>
+    <t>Solar Thermal Installers and Technicians</t>
+  </si>
+  <si>
+    <t>Installer | Solar Energy Technician | Solar Hot Water Installer (SHW Installer) | Solar Installer | Solar Maintenance Technician | Solar System Installer | Solar Technician | Solar Thermal Installer</t>
+  </si>
+  <si>
+    <t>1CadCam Unigraphics | Adobe Photoshop | Autodesk AutoCAD | Computer-aided drafting or design software | Cost estimating software | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Inventory control system software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic for Applications VBA | Microsoft Word | National Instruments LabVIEW | Oracle Java | PTC Pro/ENGINEER Wildfire | Salesforce software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Speaking | Active Listening | Active Learning</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Customer and Personal Service | English Language | Engineering and Technology | Education and Training | Design | Public Safety and Security | Computers and Electronics | Production and Processing | Administration and Management | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Speech Recognition | Near Vision | Extent Flexibility | Problem Sensitivity | Oral Expression | Written Comprehension | Speech Clarity | Information Ordering | Flexibility of Closure | Selective Attention | Arm-Hand Steadiness | Visual Color Discrimination | Far Vision | Finger Dexterity | Visualization | Trunk Strength | Manual Dexterity | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Written Expression</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | Time Pressure | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Outdoors, Exposed to All Weather Conditions | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Health and Safety of Other Workers | Indoors, Not Environmentally Controlled | Exposed to High Places | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work Outcomes and Results of Other Workers | Spend Time Standing | In an Enclosed Vehicle or Operate Enclosed Equipment | E-Mail</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Engineers | Energy Engineers, Except Wind and Solar | Geothermal Technicians | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Hydroelectric Plant Technicians | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Maintenance and Repair Workers, General | Mechanical Engineers | Plumbers, Pipefitters, and Steamfitters | Power Plant Operators | Solar Energy Installation Managers | Solar Energy Systems Engineers | Solar Photovoltaic Installers | Weatherization Installers and Technicians | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Install or repair solar energy systems designed to collect, store, and circulate solar-heated water for residential, commercial or industrial use.</t>
+  </si>
+  <si>
+    <t>Apply operation or identification tags or labels to system components, as required. | Apply ultraviolet radiation protection to prevent degradation of plumbing. | Apply weather seal, such as pipe flashings and sealants, to roof penetrations and structural devices. | Assess collector sites to ensure structural integrity of potential mounting surfaces or the best orientation and tilt for solar collectors. | Connect water heaters and storage tanks to power and water sources. | Cut, miter, and glue piping insulation to insulate plumbing pipes and fittings. | Demonstrate start-up, shut-down, maintenance, diagnostic, and safety procedures to thermal system owners. | Design active direct or indirect, passive direct or indirect, or pool solar systems. | Determine locations for installing solar subsystem components, including piping, water heaters, valves, and ancillary equipment. | Fill water tanks and check tanks, pipes, and fittings for leaks. | Identify plumbing, electrical, environmental, or safety hazards associated with solar thermal installations. | Install circulating pumps using pipe, fittings, soldering equipment, electrical supplies, and hand tools. | Install copper or plastic plumbing using pipes, fittings, pipe cutters, acetylene torches, solder, wire brushes, sand cloths, flux, plastic pipe cleaners, or plastic glue. | Install flat-plat, evacuated glass, or concentrating solar collectors on mounting devices, using brackets or struts. | Install heat exchangers and heat exchanger fluids according to installation manuals and schematics. | Install monitoring system components, such as flow meters, temperature gauges, and pressure gauges, according to system design and manufacturer specifications. | Install plumbing, such as dip tubes, port fittings, drain tank valves, pressure temperature relief valves, or tanks, according to manufacturer specifications and building codes. | Install solar collector mounting devices on tile, asphalt, shingle, or built-up gravel roofs, using appropriate materials and penetration methods. | Install solar thermal system controllers and sensors. | Perform routine maintenance or repairs to restore solar thermal systems to baseline operating conditions. | Test operation or functionality of mechanical, plumbing, electrical, and control systems.</t>
+  </si>
+  <si>
+    <t>47-2161.00</t>
+  </si>
+  <si>
+    <t>Plasterers and Stucco Masons</t>
+  </si>
+  <si>
+    <t>Applicator | Artisan Plasterer | Plaster Applicator | Plaster Mechanic | Plaster and Stucco Worker | Plasterer | Plasterer Journeyman | Plastering Contractor</t>
+  </si>
+  <si>
+    <t>A-Systems JobView | Autodesk 3ds Max Design | Autodesk Maya | Construction Software Center EasyEst | Corel Paint Shop Pro | Corel Painter | Cost estimating software | Dassault Systemes CATIA | Embedded systems development software | IBM Maximo Asset Management | Linux | Microsoft Excel | Microsoft Office software | Microsoft Word | Oracle Database | Sage Construction Anywhere | Salesforce software | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Building and Construction | Administration and Management | Design | English Language | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Manual Dexterity | Extent Flexibility | Trunk Strength | Multilimb Coordination | Static Strength | Gross Body Equilibrium | Oral Expression | Problem Sensitivity | Stamina | Dynamic Strength | Visualization | Speech Clarity | Visual Color Discrimination | Gross Body Coordination | Control Precision | Finger Dexterity | Information Ordering | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Outdoors, Exposed to All Weather Conditions | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Contact With Others | Spend Time Making Repetitive Motions | Exposed to Hazardous Equipment | Health and Safety of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Furniture Finishers | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Molders, Shapers, and Casters, Except Metal and Plastic | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Roofers | Tapers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Apply interior or exterior plaster, cement, stucco, or similar materials. May also set ornamental plaster.</t>
+  </si>
+  <si>
+    <t>Apply coats of plaster or stucco to walls, ceilings, or partitions of buildings, using trowels, brushes, or spray guns. | Apply insulation to building exteriors by installing prefabricated insulation systems over existing walls or by covering the outer wall with insulation board, reinforcing mesh, and a base coat. | Apply weatherproof, decorative coverings to exterior surfaces of buildings, such as by troweling or spraying on coats of stucco. | Clean and prepare surfaces for applications of plaster, cement, stucco, or similar materials, such as by drywall taping. | Clean job sites. | Cover surfaces such as windows, doors, or sidewalks to protect from splashing. | Create decorative textures in finish coat, using brushes or trowels, sand, pebbles, or stones. | Cure freshly plastered surfaces. | Determine materials needed to complete the job and place orders accordingly. | Install guide wires on exterior surfaces of buildings to indicate thickness of plaster or stucco and nail wire mesh, lath, or similar materials to the outside surface to hold stucco in place. | Mix mortar and plaster to desired consistency or direct workers who perform mixing. | Mold or install ornamental plaster pieces, panels, or trim. | Rough the undercoat surface with a scratcher so the finish coat will adhere. | Set up scaffolds. | Spray acoustic materials or texture finish over walls or ceilings.</t>
+  </si>
+  <si>
+    <t>47-2171.00</t>
+  </si>
+  <si>
+    <t>Reinforcing Iron and Rebar Workers</t>
+  </si>
+  <si>
+    <t>Field Ironworker | Iron Installer | Iron Worker | Ironworker | Reinforced Ironworker | Rodbuster | Rodman | Steel Tier</t>
+  </si>
+  <si>
+    <t>Application Software SHEAR | Applied Systems Associates aSa Rebar | OTP ArmaCAD | RebarWin</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mathematics | Administration and Management | Design | English Language | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Static Strength | Multilimb Coordination | Manual Dexterity | Extent Flexibility | Arm-Hand Steadiness | Stamina | Near Vision | Finger Dexterity | Control Precision | Reaction Time | Problem Sensitivity | Dynamic Strength | Gross Body Equilibrium | Gross Body Coordination | Visualization | Category Flexibility | Information Ordering | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Contact With Others | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Spend Time Standing | Spend Time Bending or Twisting Your Body | Coordinate or Lead Others in Accomplishing Work Activities | Telephone Conversations | Level of Competition | Spend Time Walking or Running | Physical Proximity | Exposed to Contaminants | Exposed to High Places | Impact of Decisions on Co-workers or Company Results | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Fence Erectors | Foundry Mold and Coremakers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Layout Workers, Metal and Plastic | Millwrights | Pipelayers | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Position and secure steel bars or mesh in concrete forms in order to reinforce concrete. Use a variety of fasteners, rod-bending machines, blowtorches, and hand tools. Includes rod busters.</t>
+  </si>
+  <si>
+    <t>Bend steel rods with hand tools or rod-bending machines and weld them with arc-welding equipment. | Cut and fit wire mesh or fabric, using hooked rods, and position fabric or mesh in concrete to reinforce concrete. | Cut rods to required lengths, using metal shears, hacksaws, bar cutters, or acetylene torches. | Determine quantities, sizes, shapes, and locations of reinforcing rods from blueprints, sketches, or oral instructions. | Place blocks under rebar to hold the bars off the deck when reinforcing floors. | Position and secure steel bars, rods, cables, or mesh in concrete forms, using fasteners, rod-bending machines, blowtorches, or hand tools. | Space and fasten together rods in forms according to blueprints, using wire and pliers.</t>
+  </si>
+  <si>
+    <t>47-2181.00</t>
+  </si>
+  <si>
+    <t>Roofers</t>
+  </si>
+  <si>
+    <t>Commercial Roofer | Industrial Roofer | Metal Roofing Mechanic | Residential Roofer | Roof Mechanic | Roof Service Technician | Roofer | Roofing Technician | Sheet Metal Roofer</t>
+  </si>
+  <si>
+    <t>ASR Software LWC-Plus | ASR Software Taper-Plus | ASR Software TopView LE | ASR Software TopView ME | AppliCad Roof Wizard | CADAFIS | DigiTools Roof CAD | Energy cost evaluation software | Exele TopView | Humidity and vapor drive calculation software | Insight Direct ServiceCEO | Maintenance record software | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | Roof Pro Estimate Software Roof Pro | RoofLogic | Roofing Calculator | Wintac Pro | Ziatek RoofDraw</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | English Language | Public Safety and Security | Education and Training | Mathematics | Design | Mechanical | Administration and Management</t>
+  </si>
+  <si>
+    <t>Gross Body Equilibrium | Extent Flexibility | Trunk Strength | Problem Sensitivity | Near Vision | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Oral Comprehension | Gross Body Coordination | Stamina | Static Strength | Control Precision | Finger Dexterity | Far Vision | Speech Recognition | Selective Attention | Visualization | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Exposed to High Places | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Exposed to Very Hot or Cold Temperatures | Time Pressure | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Physical Proximity | Determine Tasks, Priorities and Goals | Level of Competition | Frequency of Decision Making | Spend Time Standing | Indoors, Not Environmentally Controlled | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings | Impact of Decisions on Co-workers or Company Results | Spend Time Making Repetitive Motions | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Glaziers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Painters, Construction and Maintenance | Plasterers and Stucco Masons | Sheet Metal Workers | Structural Iron and Steel Workers | Tapers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Cover roofs of structures with shingles, slate, asphalt, aluminum, wood, or related materials. May spray roofs, sidings, and walls with material to bind, seal, insulate, or soundproof sections of structures.</t>
+  </si>
+  <si>
+    <t>Apply alternate layers of hot asphalt or tar and roofing paper to roofs. | Apply gravel or pebbles over top layers of roofs, using rakes or stiff-bristled brooms. | Apply modular soil- and plant-containing grids over existing roof membranes to create green roofs. | Apply plastic coatings, membranes, fiberglass, or felt over sloped roofs before applying shingles. | Apply reflective roof coatings, such as special paints or single-ply roofing sheets, to existing roofs to reduce solar heat absorption. | Attach roofing paper to roofs in overlapping strips to form bases for other materials. | Attach solar panels to existing roofs, according to specifications and without damaging roofing materials or the structural integrity of buildings. | Cement or nail flashing strips of metal or shingle over joints to make them watertight. | Cover exposed nailheads with roofing cement or caulking to prevent water leakage or rust. | Cover roofs or exterior walls of structures with slate, asphalt, aluminum, wood, gravel, gypsum, or related materials, using brushes, knives, punches, hammers, or other tools. | Cut felt, shingles, or strips of flashing to fit angles formed by walls, vents, or intersecting roof surfaces. | Estimate materials and labor required to complete roofing jobs. | Glaze top layers to make a smooth finish or embed gravel in the bitumen for rough surfaces. | Inspect problem roofs to determine the best repair procedures. | Install attic ventilation systems, such as turbine vents, gable or ridge vents, or conventional or solar-powered exhaust fans. | Install layers of vegetation-based green roofs, including protective membranes, drainage, aeration, water retention and filter layers, soil substrates, irrigation materials, and plants. | Install partially overlapping layers of material over roof insulation surfaces, using chalk lines, gauges on shingling hatchets, or lines on shingles. | Install skylights on roofs to increase natural light inside structures or to reduce energy costs. | Install vapor barriers or layers of insulation on flat roofs. | Install, repair, or replace single-ply roofing systems, using waterproof sheet materials such as modified plastics, elastomeric, or other asphaltic compositions. | Mop or pour hot asphalt or tar onto roof bases. | Punch holes in slate, tile, terra cotta, or wooden shingles, using punches and hammers. | Remove snow, water, or debris from roofs prior to applying roofing materials. | Set up scaffolding to provide safe access to roofs. | Smooth rough spots to prepare surfaces for waterproofing, using hammers, chisels, or rubbing bricks. | Spray roofs, sidings, or walls to bind, seal, insulate, or soundproof sections of structures, using spray guns, air compressors, or heaters. | Waterproof or damp-proof walls, floors, roofs, foundations, or basements by painting or spraying surfaces with waterproof coatings or by attaching waterproofing membranes to surfaces.</t>
+  </si>
+  <si>
+    <t>47-2211.00</t>
+  </si>
+  <si>
+    <t>Sheet Metal Workers</t>
+  </si>
+  <si>
+    <t>Commercial Sheet Metal Service Installer | Field Installer | HVAC Sheet Metal Installer (Heating, Ventilation, and Air Conditioning Sheet Metal Installer) | HVAC Sheet Metal Specialist (Heating, Ventilation, and Air Conditioning Sheet Metal Specialist) | Sheet Metal Fabricator | Sheet Metal Installer | Sheet Metal Journeyman | Sheet Metal Layout Mechanic | Sheet Metal Mechanic | Sheet Metal Worker</t>
+  </si>
+  <si>
+    <t>Applied Production ProFab | Applied Production ProFold | Autodesk AutoCAD | Corte Certo | FCC Software AutoPOL Series | JETCAM Expert | Merry Mechanization SMP/IS | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | PTC Creo Parametric | QuickPen DuctDesigner 3D | Revcad Software Sheet Lightning | Siemens NX | Striker Systems SS-Profile | WiCAM PN4000 | XY Soft Sheet Cutting Suite</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Critical Thinking | Mathematics | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Mathematics | Design | English Language | Education and Training | Administration and Management | Production and Processing | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Visualization | Near Vision | Multilimb Coordination | Manual Dexterity | Arm-Hand Steadiness | Information Ordering | Selective Attention | Finger Dexterity | Flexibility of Closure | Category Flexibility | Deductive Reasoning | Problem Sensitivity | Oral Expression | Written Comprehension | Oral Comprehension | Trunk Strength | Static Strength | Control Precision | Speech Clarity | Speech Recognition | Auditory Attention | Depth Perception | Far Vision | Extent Flexibility | Reaction Time | Perceptual Speed | Number Facility | Mathematical Reasoning | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Minor Burns, Cuts, Bites, or Stings | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Time Pressure | Consequence of Error | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Spend Time Bending or Twisting Your Body | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Hazardous Equipment | Indoors, Not Environmentally Controlled | Pace Determined by Speed of Equipment</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Carpenters | Drywall and Ceiling Tile Installers | Electrical and Electronic Equipment Assemblers | Engine and Other Machine Assemblers | Grinding and Polishing Workers, Hand | Industrial Machinery Mechanics | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Layout Workers, Metal and Plastic | Model Makers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Plumbers, Pipefitters, and Steamfitters | Reinforcing Iron and Rebar Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Fabricate, assemble, install, and repair sheet metal products and equipment, such as ducts, control boxes, drainpipes, and furnace casings. Work may involve any of the following: setting up and operating fabricating machines to cut, bend, and straighten sheet metal; shaping metal over anvils, blocks, or forms using hammer; operating soldering and welding equipment to join sheet metal parts; or inspecting, assembling, and smoothing seams and joints of burred surfaces. Includes sheet metal duct installers who install prefabricated sheet metal ducts used for heating, air conditioning, or other purposes.</t>
+  </si>
+  <si>
+    <t>Convert blueprints into shop drawings to be followed in the construction or assembly of sheet metal products. | Determine project requirements, such as scope, assembly sequences, or required methods or materials, using blueprints, drawings, or written or verbal instructions. | Fabricate ducts for high efficiency heating, ventilating, and air conditioning (HVAC) systems to maximize efficiency of systems. | Fabricate or alter parts at construction sites, using shears, hammers, punches, or drills. | Fasten roof panel edges or machine-made moldings to structures by nailing or welding. | Fasten seams or joints together with welds, bolts, cement, rivets, solder, caulks, metal drive clips, or bonds to assemble components into products or to repair sheet metal items. | Finish parts, using hacksaws or hand, rotary, or squaring shears. | Hire, train, or supervise new employees or apprentices. | Inspect individual parts, assemblies, or installations, using measuring instruments, such as calipers, scales, or micrometers. | Install assemblies, such as flashing, pipes, tubes, heating and air conditioning ducts, furnace casings, rain gutters, or downspouts in supportive frameworks. | Lay out, measure, and mark dimensions and reference lines on material, such as roofing panels, using calculators, scribes, dividers, squares, or rulers. | Maintain equipment, making repairs or modifications when necessary. | Maneuver completed roofing units into position for installation. | Perform building commissioning activities by completing mechanical inspections of a building's water, lighting, or heating, ventilating, and air conditioning (HVAC) systems. | Select gauges or types of sheet metal or nonmetallic material, according to product specifications. | Shape metal material over anvils, blocks, or other forms, using hand tools. | Transport prefabricated parts to construction sites for assembly and installation. | Trim, file, grind, deburr, buff, or smooth surfaces, seams, or joints of assembled parts, using hand tools or portable power tools. | Verify that heating, ventilating, and air conditioning (HVAC) systems are designed, installed, and calibrated in accordance with green certification standards, such as those of Leadership in Energy and Environmental Design (LEED).</t>
+  </si>
+  <si>
+    <t>47-2221.00</t>
+  </si>
+  <si>
+    <t>Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Fitter | Iron Worker | Ironworker | Steel Fabricator | Steel Worker | Structural Steel Erector | Tower Hand</t>
+  </si>
+  <si>
+    <t>Cost estimating software | Inventory tracking software | Microsoft Outlook | Project scheduling software | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Active Learning | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Mathematics | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Static Strength | Arm-Hand Steadiness | Manual Dexterity | Near Vision | Visualization | Control Precision | Trunk Strength | Extent Flexibility | Gross Body Equilibrium | Depth Perception | Problem Sensitivity | Selective Attention | Dynamic Strength | Far Vision | Finger Dexterity | Stamina | Reaction Time | Rate Control | Information Ordering | Auditory Attention | Hearing Sensitivity | Oral Comprehension | Deductive Reasoning | Oral Expression | Gross Body Coordination | Response Orientation | Speech Clarity | Speech Recognition | Glare Sensitivity | Time Sharing | Perceptual Speed | Category Flexibility | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to High Places | Spend Time Standing | Exposed to Very Hot or Cold Temperatures | Physical Proximity | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Contaminants | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Hazardous Equipment | Time Pressure | Exposed to Minor Burns, Cuts, Bites, or Stings | Importance of Being Exact or Accurate | Exposed to Extremely Bright or Inadequate Lighting Conditions | Work Outcomes and Results of Other Workers | In an Open Vehicle or Operating Equipment | Exposed to Cramped Work Space, Awkward Positions | Spend Time Walking or Running | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Spend Time Bending or Twisting Your Body | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition | Consequence of Error | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Layout Workers, Metal and Plastic | Maintenance and Repair Workers, General | Millwrights | Pipelayers | Plumbers, Pipefitters, and Steamfitters | Reinforcing Iron and Rebar Workers | Riggers | Sheet Metal Workers | Structural Metal Fabricators and Fitters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Raise, place, and unite iron or steel girders, columns, and other structural members to form completed structures or structural frameworks. May erect metal storage tanks and assemble prefabricated metal buildings.</t>
+  </si>
+  <si>
+    <t>Assemble hoisting equipment or rigging, such as cables, pulleys, or hooks, to move heavy equipment or materials. | Bolt aligned structural steel members in position for permanent riveting, bolting, or welding into place. | Connect columns, beams, and girders with bolts, following blueprints and instructions from supervisors. | Cut, bend, or weld steel pieces, using metal shears, torches, or welding equipment. | Dismantle structures or equipment. | Drive drift pins through rivet holes to align rivet holes in structural steel members with corresponding holes in previously placed members. | Erect metal or precast concrete components for structures, such as buildings, bridges, dams, towers, storage tanks, fences, or highway guard rails. | Fabricate metal parts, such as steel frames, columns, beams, or girders, according to blueprints or instructions from supervisors. | Fasten structural steel members to hoist cables, using chains, cables, or rope. | Force structural steel members into final positions, using turnbuckles, crowbars, jacks, or hand tools. | Hoist steel beams, girders, or columns into place, using cranes or signaling hoisting equipment operators to lift and position structural steel members. | Hold rivets while riveters use air hammers to form heads on rivets. | Insert sealing strips, wiring, insulating material, ladders, flanges, gauges, or valves, depending on types of structures being assembled. | Place blocks under reinforcing bars used to reinforce floors. | Pull, push, or pry structural steel members into approximate positions for bolting into place. | Read specifications or blueprints to determine the locations, quantities, or sizes of materials required. | Ride on girders or other structural steel members to position them, or use rope to guide them into position. | Unload and position prefabricated steel units for hoisting, as needed. | Verify vertical and horizontal alignment of structural steel members, using plumb bobs, laser equipment, transits, or levels.</t>
+  </si>
+  <si>
+    <t>47-2231.00</t>
+  </si>
+  <si>
+    <t>Solar Photovoltaic Installers</t>
+  </si>
+  <si>
+    <t>Journeyman Electrician PV Installer (Journeyman Electrician Photovoltaic Installer) | PV Installation Tech (Photovoltaic Installation Technician) | PV Installer (Photovoltaic Installer) | Solar Designer | Solar Electric Installer | Solar Installer | Solar PV Installer (Solar Photovoltaic Installer) | Solar PV Integrator (Solar Photovoltaic Integrator) | Solar Panel Installation Technician (Solar Panel Installation Tech) | Solar Technician (Solar Tech)</t>
+  </si>
+  <si>
+    <t>Cost estimating software | Extensible markup language XML | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Salesforce software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Monitoring | Reading Comprehension | Active Learning</t>
+  </si>
+  <si>
+    <t>Building and Construction | Engineering and Technology | Mechanical | Design | Administration and Management | Customer and Personal Service | Mathematics | Public Safety and Security | Education and Training | Production and Processing | English Language | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Visualization | Information Ordering | Oral Comprehension | Deductive Reasoning | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Extent Flexibility | Trunk Strength | Static Strength | Multilimb Coordination | Perceptual Speed | Oral Expression | Gross Body Equilibrium | Control Precision | Selective Attention | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to High Places | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Physical Proximity | Contact With Others | Spend Time Standing | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Work Outcomes and Results of Other Workers | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Spend Time Keeping or Regaining Balance | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | Indoors, Not Environmentally Controlled | Time Pressure | Spend Time Making Repetitive Motions | Conflict Situations | Outdoors, Under Cover | E-Mail | Exposed to Cramped Work Space, Awkward Positions | Importance of Repeating Same Tasks | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Electric Motor, Power Tool, and Related Repairers | Electrical Engineers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electricians | Energy Engineers, Except Wind and Solar | Geothermal Technicians | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Hydroelectric Plant Technicians | Lighting Technicians | Maintenance and Repair Workers, General | Mechanical Engineers | Plumbers, Pipefitters, and Steamfitters | Solar Energy Installation Managers | Solar Energy Systems Engineers | Solar Sales Representatives and Assessors | Solar Thermal Installers and Technicians | Wind Energy Engineers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Assemble, install, or maintain solar photovoltaic (PV) systems on roofs or other structures in compliance with site assessment and schematics. May include measuring, cutting, assembling, and bolting structural framing and solar modules. May perform minor electrical work such as current checks.</t>
+  </si>
+  <si>
+    <t>Activate photovoltaic (PV) systems to verify system functionality and conformity to performance expectations. | Apply weather sealing to array, building, or support mechanisms. | Assemble solar modules, panels, or support structures, as specified. | Check electrical installation for proper wiring, polarity, grounding, or integrity of terminations. | Compile or maintain records of system operation, performance, and maintenance. | Demonstrate system functionality and performance, including start-up, shut-down, normal operation, and emergency or bypass operations. | Determine appropriate sizes, ratings, and locations for all system overcurrent devices, disconnect devices, grounding equipment, and surge suppression equipment. | Determine connection interfaces for additional subpanels or for connecting photovoltaic (PV) systems with utility services or other power generation sources. | Determine materials, equipment, and installation sequences necessary to maximize installation efficiency. | Determine photovoltaic (PV) system designs or configurations based on factors such as customer needs, expectations, and site conditions. | Diagram layouts and locations for photovoltaic (PV) arrays and equipment, including existing building or site features. | Examine designs to determine current requirements for all parts of the photovoltaic (PV) system electrical circuit. | Identify and resolve any deficiencies in photovoltaic (PV) system installation or materials. | Identify electrical, environmental, and safety hazards associated with photovoltaic (PV) installations. | Identify installation locations with proper orientation, area, solar access, or structural integrity for photovoltaic (PV) arrays. | Identify methods for laying out, orienting, and mounting modules or arrays to ensure efficient installation, electrical configuration, or system maintenance. | Install active solar systems, including solar collectors, concentrators, pumps, or fans. | Install module array interconnect wiring, implementing measures to disable arrays during installation. | Install photovoltaic (PV) systems in accordance with codes and standards, using drawings, schematics, and instructions. | Install required labels on solar system components and hardware. | Measure and analyze system performance and operating parameters to assess operating condition of systems or equipment. | Perform routine photovoltaic (PV) system maintenance on modules, arrays, batteries, power conditioning equipment, safety systems, structural systems, weather sealing, or balance of systems equipment. | Program, adjust, or configure inverters and controls for desired set points and operating modes. | Select mechanical designs, installation equipment, or installation plans that conform to environmental, architectural, structural, site, and code requirements. | Test operating voltages to ensure operation within acceptable limits for power conditioning equipment, such as inverters and controllers. | Visually inspect and test photovoltaic (PV) modules or systems.</t>
+  </si>
+  <si>
+    <t>47-3011.00</t>
+  </si>
+  <si>
+    <t>Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters</t>
+  </si>
+  <si>
+    <t>Bricklayer Helper | Hod Carrier | Marble Finisher Helper | Mason Tender | Restoration Labor Mason Tender</t>
+  </si>
+  <si>
+    <t>Autodesk Revit | Aya Associates Comp-U-Floor | CPR Visual Estimator | Computer aided design and drafting CADD software | Construction Management Software ProEst | Daystar iStructural.com | EasyCAD Iris 2D | Intuit QuickBooks | Measure Square FloorEstimate Pro | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Word | RISA Technologies RISAMasonry | TileGem | Tradesman's Software Master Estimator</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Design | Mathematics</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Static Strength | Multilimb Coordination | Arm-Hand Steadiness | Near Vision | Extent Flexibility | Far Vision | Manual Dexterity | Visualization | Information Ordering | Depth Perception | Gross Body Equilibrium | Stamina | Dynamic Strength | Speed of Limb Movement | Control Precision | Finger Dexterity | Deductive Reasoning | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Exposed to Contaminants | Spend Time Standing | Outdoors, Exposed to All Weather Conditions | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Exposed to High Places | Exposed to Hazardous Equipment | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Spend Time Bending or Twisting Your Body | Exposed to Very Hot or Cold Temperatures | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Telephone Conversations | Spend Time Climbing Ladders, Scaffolds, or Poles | Level of Competition | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Contact With Others | Spend Time Walking or Running | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Helpers--Carpenters | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Production Workers | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Plasterers and Stucco Masons | Refractory Materials Repairers, Except Brickmasons | Stonemasons | Structural Iron and Steel Workers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Help brickmasons, blockmasons, stonemasons, or tile and marble setters by performing duties requiring less skill. Duties include using, supplying, or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Apply caulk, sealants, or other agents to installed surfaces. | Apply grout between joints of bricks or tiles, using grouting trowels. | Arrange or store materials, machines, tools, or equipment. | Clean installation surfaces, equipment, tools, work sites, or storage areas, using water, chemical solutions, oxygen lances, or polishing machines. | Correct surface imperfections or fill chipped, cracked, or broken bricks or tiles, using fillers, adhesives, or grouting materials. | Cut materials to specified sizes for installation, using power saws or tile cutters. | Erect scaffolding or other installation structures. | Locate and supply materials to masons for installation, following drawings or numbered sequences. | Mix mortar, plaster, and grout, manually or using machines, according to standard formulas. | Modify material moving, mixing, grouting, grinding, polishing, or cleaning procedures, according to installation or material requirements. | Move or position materials such as marble slabs, using cranes, hoists, or dollies. | Provide assistance in the preparation, installation, repair, or rebuilding of tile, brick, or stone surfaces. | Remove damaged tile, brick, or mortar, and clean or prepare surfaces, using pliers, hammers, chisels, drills, wire brushes, or metal wire anchors. | Remove excess grout or residue from tile or brick joints, using sponges or trowels. | Transport materials, tools, or machines to installation sites, manually or using conveyance equipment.</t>
+  </si>
+  <si>
+    <t>47-3012.00</t>
+  </si>
+  <si>
+    <t>Helpers--Carpenters</t>
+  </si>
+  <si>
+    <t>Carpenter Assistant | Carpenter Helper | Carpenter's Helper</t>
+  </si>
+  <si>
+    <t>Bosch Punch List | Cost estimating software | Craftsman CD Estimator | Drawing and drafting software | Intuit QuickBooks | Job costing software | Linux | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Quicken | SAP software | Salesforce software | Turtle Creek Software Goldenseal | UNIX</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Mathematics | Transportation | English Language | Customer and Personal Service | Production and Processing | Design | Public Safety and Security | Administration and Management | Education and Training | Telecommunications</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Manual Dexterity | Problem Sensitivity | Extent Flexibility | Static Strength | Multilimb Coordination | Speech Clarity | Speech Recognition | Depth Perception | Trunk Strength | Reaction Time | Control Precision | Finger Dexterity | Selective Attention | Visualization | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Equipment | Contact With Others | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Outdoors, Exposed to All Weather Conditions | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Physical Proximity | Time Pressure | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Spend Time Making Repetitive Motions | Telephone Conversations | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Exposed to Cramped Work Space, Awkward Positions | Consequence of Error | Spend Time Bending or Twisting Your Body | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Level of Competition</t>
+  </si>
+  <si>
+    <t>Boilermakers | Brickmasons and Blockmasons | Cabinetmakers and Bench Carpenters | Carpenters | Cement Masons and Concrete Finishers | Drywall and Ceiling Tile Installers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Production Workers | Helpers--Roofers | Layout Workers, Metal and Plastic | Plasterers and Stucco Masons | Reinforcing Iron and Rebar Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers</t>
+  </si>
+  <si>
+    <t>Help carpenters by performing duties requiring less skill. Duties include using, supplying, or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Align, straighten, plumb, or square forms for installation. | Clean work areas, machines, or equipment, to maintain a clean and safe job site. | Construct forms and assist in raising them to the required elevation. | Cover surfaces with laminated plastic covering material. | Cut and install insulating or sound-absorbing material. | Cut tile or linoleum to fit and spread adhesives on flooring for installation. | Cut timbers, lumber, or paneling to specified dimensions. | Drill holes in timbers or lumber. | Erect scaffolding, shoring, or braces. | Fasten timbers or lumber with glue, screws, pegs, or nails and install hardware. | Glue and clamp edges or joints of assembled parts. | Hold plumb bobs, sighting rods, or other equipment to aid in establishing reference points and lines. | Install handrails under the direction of a carpenter. | Perform tie spacing layout and measure, mark, drill or cut. | Position and hold timbers, lumber, or paneling in place for fastening or cutting. | Secure stakes to grids for constructions of footings, nail scabs to footing forms, and vibrate and float concrete. | Select tools, equipment, or materials from storage and transport items to work site. | Smooth or sand surfaces to remove ridges, tool marks, glue, or caulking.</t>
+  </si>
+  <si>
+    <t>47-3013.00</t>
+  </si>
+  <si>
+    <t>Helpers--Electricians</t>
+  </si>
+  <si>
+    <t>Apprentice | E and I Apprentice (Electrical and Instrumentation Apprentice) | E and I Apprentice (Electrician and Instrumentation Apprentice) | Electrical Apprentice | Electrical Helper | Electrician Apprentice | Electrician Helper | Electrician's Helper | Inside Wireman Apprentice | Wireman Apprentice</t>
+  </si>
+  <si>
+    <t>Computer-aided drafting or design software | Microsoft Excel | Microsoft Office software | Recordkeeping software | Report generation software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | Public Safety and Security | Design | Customer and Personal Service | Administration and Management | Education and Training | English Language | Mathematics | Engineering and Technology | Physics | Transportation</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Extent Flexibility | Finger Dexterity | Arm-Hand Steadiness | Problem Sensitivity | Control Precision | Multilimb Coordination | Trunk Strength | Visual Color Discrimination | Oral Expression | Oral Comprehension | Speech Recognition | Selective Attention | Information Ordering | Deductive Reasoning | Speech Clarity | Gross Body Equilibrium | Visualization</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Cramped Work Space, Awkward Positions | Importance of Being Exact or Accurate | Physical Proximity | Exposed to Hazardous Equipment | Exposed to Contaminants | Spend Time Walking or Running | Outdoors, Exposed to All Weather Conditions | Time Pressure | Spend Time Climbing Ladders, Scaffolds, or Poles | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Spend Time Kneeling, Crouching, Stooping, or Crawling | Outdoors, Under Cover | Frequency of Decision Making | Exposed to Hazardous Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Freedom to Make Decisions | Telephone Conversations</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Carpenters | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electricians | Helpers--Carpenters | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Lighting Technicians | Maintenance and Repair Workers, General | Millwrights | Plumbers, Pipefitters, and Steamfitters | Riggers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters</t>
+  </si>
+  <si>
+    <t>Help electricians by performing duties requiring less skill. Duties include using, supplying, or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Bolt component parts together to form tower assemblies, using hand tools. | Break up concrete, using airhammer, to facilitate installation, construction, or repair of equipment. | Clean work area and wash parts. | Construct controllers and panels, using power drills, drill presses, taps, saws, and punches. | Dig trenches or holes for installation of conduit or supports. | Disassemble defective electrical equipment, replace defective or worn parts, and reassemble equipment, using hand tools. | Drill holes and pull or push wiring through openings, using hand and power tools. | Erect electrical system components and barricades, and rig scaffolds, hoists, and shoring. | Examine electrical units for loose connections and broken insulation and tighten connections, using hand tools. | Install copper-clad ground rods, using a manual post driver. | Maintain tools, vehicles, and equipment and keep parts and supplies in order. | Measure, cut, and bend wire and conduit, using measuring instruments and hand tools. | Operate cutting torches and welding equipment, while working with conduit and metal components to construct devices associated with electrical functions. | Operate heavy equipment, such as backhoes. | Paint a variety of objects related to electrical functions. | Perform semi-skilled and unskilled laboring duties related to the installation, maintenance and repair of a wide variety of electrical systems and equipment. | Raise, lower, or position equipment, tools, and materials, using hoist, hand line, or block and tackle. | Requisition materials, using warehouse requisition or release forms. | Solder electrical connections, using soldering iron. | String transmission lines or cables through ducts or conduits, under the ground, through equipment, or to towers. | Strip insulation from wire ends, using wire stripping pliers, and attach wires to terminals for subsequent soldering. | Thread conduit ends, connect couplings, and fabricate and secure conduit support brackets, using hand tools. | Trace out short circuits in wiring, using test meter. | Transport tools, materials, equipment, and supplies to work site by hand, handtruck, or heavy, motorized truck. | Trim trees and clear undergrowth along right-of-way.</t>
+  </si>
+  <si>
+    <t>47-3014.00</t>
+  </si>
+  <si>
+    <t>Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons</t>
+  </si>
+  <si>
+    <t>Painter Helper | Plaster Helper | Plaster Tender</t>
+  </si>
+  <si>
+    <t>A-Systems JobView | Apple iWork | Construction Software Center EasyEst | Cost estimating software | Evergreen Technology Eagle Bid Estimating | Microsoft Excel | Microsoft Office software | On Center Quick Bid | Sage Construction Anywhere | Turtle Creek Software Goldenseal</t>
+  </si>
+  <si>
+    <t>Building and Construction | English Language</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Gross Body Equilibrium | Extent Flexibility | Trunk Strength | Static Strength | Manual Dexterity | Gross Body Coordination | Multilimb Coordination | Speech Recognition | Far Vision | Near Vision | Stamina | Dynamic Strength | Finger Dexterity | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Outdoors, Exposed to All Weather Conditions | Frequency of Decision Making | Spend Time Bending or Twisting Your Body | Time Pressure | Health and Safety of Other Workers | Telephone Conversations | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Production Workers | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Paperhangers | Plasterers and Stucco Masons | Roofers | Terrazzo Workers and Finishers</t>
+  </si>
+  <si>
+    <t>Help painters, paperhangers, plasterers, or stucco masons by performing duties requiring less skill. Duties include using, supplying, or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Apply protective coverings, such as masking tape, to articles or areas that could be damaged or stained by work processes. | Clean work areas and equipment. | Erect scaffolding. | Fill cracks or breaks in surfaces of plaster articles or areas with putty or epoxy compounds. | Mix plaster, and carry plaster to plasterers. | Perform support duties to assist painters, paperhangers, plasterers, or masons. | Place articles to be stripped into stripping tanks. | Pour specified amounts of chemical solutions into stripping tanks. | Remove articles such as cabinets, metal furniture, and paint containers from stripping tanks after prescribed periods of time. | Smooth surfaces of articles to be painted, using sanding and buffing tools and equipment. | Supply or hold tools and materials.</t>
+  </si>
+  <si>
+    <t>47-3015.00</t>
+  </si>
+  <si>
+    <t>Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters</t>
+  </si>
+  <si>
+    <t>Plumber's Helper</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | Mechanical | Mathematics | English Language | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Multilimb Coordination | Arm-Hand Steadiness | Trunk Strength | Extent Flexibility | Near Vision | Oral Comprehension | Problem Sensitivity | Visualization | Speech Recognition | Static Strength | Control Precision | Finger Dexterity | Information Ordering | Oral Expression</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Bending or Twisting Your Body | Exposed to Cramped Work Space, Awkward Positions | Work With or Contribute to a Work Group or Team | Time Pressure | Spend Time Kneeling, Crouching, Stooping, or Crawling | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Physical Proximity | Indoors, Not Environmentally Controlled | Telephone Conversations | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Boilermakers | Carpenters | Construction Laborers | Drywall and Ceiling Tile Installers | Electricians | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Maintenance and Repair Workers, General | Millwrights | Pipelayers | Plumbers, Pipefitters, and Steamfitters | Septic Tank Servicers and Sewer Pipe Cleaners | Sheet Metal Workers | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Help plumbers, pipefitters, steamfitters, or pipelayers by performing duties requiring less skill. Duties include using, supplying, or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Assist pipe fitters in the layout, assembly, and installation of piping for air, ammonia, gas, and water systems. | Clean and renew steam traps. | Clean shop, work area, and machines, using solvent and rags. | Cut or drill holes in walls or floors to accommodate the passage of pipes. | Cut pipe and lift up to fitters. | Disassemble and remove damaged or worn pipe. | Excavate and grade ditches, and lay and join pipe for water and sewer service. | Fill pipes with sand or resin to prevent distortion, and hold pipes during bending and installation. | Fit or assist in fitting valves, couplings, or assemblies to tanks, pumps, or systems, using hand tools. | Immerse pipe in chemical solution to remove dirt, oil, and scale. | Install gas burners to convert furnaces from wood, coal, or oil. | Measure, cut, thread and assemble new pipe, placing the assembled pipe in hangers or other supports. | Mount brackets and hangers on walls and ceilings to hold pipes, and set sleeves or inserts to provide support for pipes. | Perform rough-ins, repair and replace fixtures and water heaters, and locate, repair, or remove leaking or broken pipes. | Requisition tools and equipment, select type and size of pipe, and collect and transport materials and equipment to work site.</t>
+  </si>
+  <si>
+    <t>47-3016.00</t>
+  </si>
+  <si>
+    <t>Helpers--Roofers</t>
+  </si>
+  <si>
+    <t>Roofer Helper</t>
+  </si>
+  <si>
+    <t>AppliCad Roof Wizard | DigiTools Roof CAD | Energy cost evaluation software | Exele TopView | Humidity and vapor drive calculation software | Insight Direct ServiceCEO | Maintenance record software | Roof Pro Estimate Software Roof Pro | RoofLogic | Roofing Calculator | Wintac Pro | Ziatek RoofDraw</t>
+  </si>
+  <si>
+    <t>Building and Construction | Administration and Management | Customer and Personal Service | Public Safety and Security | Mathematics | Transportation | Mechanical | Education and Training</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Gross Body Equilibrium | Manual Dexterity | Multilimb Coordination | Speech Clarity | Problem Sensitivity | Visualization | Arm-Hand Steadiness | Finger Dexterity | Speech Recognition | Depth Perception | Extent Flexibility | Static Strength | Far Vision | Gross Body Coordination | Stamina | Flexibility of Closure | Information Ordering | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to High Places | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Spend Time Kneeling, Crouching, Stooping, or Crawling | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Impact of Decisions on Co-workers or Company Results | Spend Time Walking or Running | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Exposed to Minor Burns, Cuts, Bites, or Stings | Contact With Others</t>
+  </si>
+  <si>
+    <t>Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Painters, Construction and Maintenance | Plasterers and Stucco Masons | Roofers | Structural Iron and Steel Workers | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Help roofers by performing duties requiring less skill. Duties include using, supplying, or holding materials or tools, and cleaning work area and equipment.</t>
+  </si>
+  <si>
+    <t>Apply shingles, gravel, or asphalt over the top layer of tar to protect the roofing material. | Attach roofing paper and composition shingles, using nails. | Attach sheets of metal to roof boards or building frameworks when installing metal roofs. | Check to ensure that completed roofs are watertight. | Chop tar into small pieces, and heat chopped tar in kettles. | Clean work areas and equipment. | Clear drains and downspouts and clean gutters. | Cover roofs with layers of roofing felt or asphalt strips before installing tile, slate, or composition materials. | Hoist tar and roofing materials to roofs, using ropes and pulleys, or carry materials up ladders. | Locate worn or torn areas in roofs. | Maintain tools and equipment. | Perform emergency leak repairs and general maintenance for a variety of roof types. | Place tiles, nail them to roof boards, and cover nailheads with roofing cement. | Provide assistance to skilled roofers installing and repairing roofs, flashings, and surfaces. | Remove old roofing materials. | Set ladders, scaffolds, and hoists in place for taking supplies to roofs. | Sweep and clean roofs to prepare them for the application of new roofing materials. | Unload materials and tools from work trucks, and unroll roofing as directed.</t>
+  </si>
+  <si>
+    <t>47-3019.00</t>
+  </si>
+  <si>
+    <t>Helpers, Construction Trades, All Other</t>
+  </si>
+  <si>
+    <t>Apprentice Helper | Construction Helper | Craft Helper | Glazier Helper | Ironworker Helper | Sheet Metal Helper | Trade Helper | Tradesman Helper | Construction Trades Helper | Insulation Helper</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | English Language | Public Safety and Security | Mathematics | Production and Processing</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Health and Safety of Other Workers | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Consequence of Error | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Helpers--Carpenters | Helpers--Electricians | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Roofers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Construction Laborers | Carpenters | Electricians | Plumbers, Pipefitters, and Steamfitters | Sheet Metal Workers | Glaziers | Roofers | Insulation Workers, Mechanical | Structural Iron and Steel Workers | Reinforcing Iron and Rebar Workers | Drywall and Ceiling Tile Installers | Painters, Construction and Maintenance | First-Line Supervisors of Construction Trades and Extraction Workers | Helpers--Installation, Maintenance, and Repair Workers</t>
+  </si>
+  <si>
+    <t>All construction trades helpers not listed separately.</t>
+  </si>
+  <si>
+    <t>Assist construction trades workers in specialties not classified separately. | Carry, position, and hold materials, tools, and equipment for craft workers. | Measure, cut, and prepare materials according to instructions. | Erect, move, and dismantle scaffolding, ladders, and temporary supports. | Clean work areas and remove debris, scrap, and surplus materials. | Load, unload, and distribute materials and supplies at the job site. | Mix mortar, grout, adhesives, and other compounds as directed. | Operate hand and power tools under the direction of skilled workers. | Set up and maintain temporary lighting, power, and barricades. | Follow safety rules and wear required personal protective equipment. | Assist with installation, fitting, and fastening of components. | Maintain tools and equipment in clean and serviceable condition. | Signal equipment operators and assist with material hoisting. | Learn trade skills through on-the-job instruction and observation.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1931,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" t="s">
+        <v>116</v>
+      </c>
+      <c r="K11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" t="s">
+        <v>127</v>
+      </c>
+      <c r="K12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" t="s">
+        <v>137</v>
+      </c>
+      <c r="K13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" t="s">
+        <v>147</v>
+      </c>
+      <c r="J14" t="s">
+        <v>148</v>
+      </c>
+      <c r="K14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" t="s">
+        <v>167</v>
+      </c>
+      <c r="H16" t="s">
+        <v>168</v>
+      </c>
+      <c r="I16" t="s">
+        <v>169</v>
+      </c>
+      <c r="J16" t="s">
+        <v>170</v>
+      </c>
+      <c r="K16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" t="s">
+        <v>180</v>
+      </c>
+      <c r="J17" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18" t="s">
+        <v>189</v>
+      </c>
+      <c r="H18" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" t="s">
+        <v>191</v>
+      </c>
+      <c r="J18" t="s">
+        <v>192</v>
+      </c>
+      <c r="K18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G19" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" t="s">
+        <v>201</v>
+      </c>
+      <c r="J19" t="s">
+        <v>202</v>
+      </c>
+      <c r="K19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G20" t="s">
+        <v>210</v>
+      </c>
+      <c r="H20" t="s">
+        <v>211</v>
+      </c>
+      <c r="I20" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" t="s">
+        <v>213</v>
+      </c>
+      <c r="K20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" t="s">
+        <v>220</v>
+      </c>
+      <c r="G21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J21" t="s">
+        <v>224</v>
+      </c>
+      <c r="K21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" t="s">
+        <v>231</v>
+      </c>
+      <c r="G22" t="s">
+        <v>232</v>
+      </c>
+      <c r="H22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J22" t="s">
+        <v>235</v>
+      </c>
+      <c r="K22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" t="s">
+        <v>243</v>
+      </c>
+      <c r="H23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I23" t="s">
+        <v>245</v>
+      </c>
+      <c r="J23" t="s">
+        <v>246</v>
+      </c>
+      <c r="K23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" t="s">
+        <v>251</v>
+      </c>
+      <c r="E24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I24" t="s">
+        <v>255</v>
+      </c>
+      <c r="J24" t="s">
+        <v>256</v>
+      </c>
+      <c r="K24" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" t="s">
+        <v>260</v>
+      </c>
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" t="s">
+        <v>263</v>
+      </c>
+      <c r="H25" t="s">
+        <v>264</v>
+      </c>
+      <c r="I25" t="s">
+        <v>265</v>
+      </c>
+      <c r="J25" t="s">
+        <v>266</v>
+      </c>
+      <c r="K25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>272</v>
+      </c>
+      <c r="G26" t="s">
+        <v>273</v>
+      </c>
+      <c r="H26" t="s">
+        <v>274</v>
+      </c>
+      <c r="I26" t="s">
+        <v>275</v>
+      </c>
+      <c r="J26" t="s">
+        <v>276</v>
+      </c>
+      <c r="K26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>278</v>
+      </c>
+      <c r="B27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C27" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" t="s">
+        <v>281</v>
+      </c>
+      <c r="E27" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" t="s">
+        <v>283</v>
+      </c>
+      <c r="G27" t="s">
+        <v>284</v>
+      </c>
+      <c r="H27" t="s">
+        <v>285</v>
+      </c>
+      <c r="I27" t="s">
+        <v>286</v>
+      </c>
+      <c r="J27" t="s">
+        <v>287</v>
+      </c>
+      <c r="K27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>289</v>
+      </c>
+      <c r="B28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" t="s">
+        <v>230</v>
+      </c>
+      <c r="F28" t="s">
+        <v>293</v>
+      </c>
+      <c r="G28" t="s">
+        <v>294</v>
+      </c>
+      <c r="H28" t="s">
+        <v>295</v>
+      </c>
+      <c r="I28" t="s">
+        <v>296</v>
+      </c>
+      <c r="J28" t="s">
+        <v>297</v>
+      </c>
+      <c r="K28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B29" t="s">
+        <v>300</v>
+      </c>
+      <c r="C29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D29" t="s">
+        <v>302</v>
+      </c>
+      <c r="E29" t="s">
+        <v>303</v>
+      </c>
+      <c r="F29" t="s">
+        <v>304</v>
+      </c>
+      <c r="G29" t="s">
+        <v>305</v>
+      </c>
+      <c r="H29" t="s">
+        <v>306</v>
+      </c>
+      <c r="I29" t="s">
+        <v>307</v>
+      </c>
+      <c r="J29" t="s">
+        <v>308</v>
+      </c>
+      <c r="K29" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" t="s">
+        <v>315</v>
+      </c>
+      <c r="G30" t="s">
+        <v>316</v>
+      </c>
+      <c r="H30" t="s">
+        <v>317</v>
+      </c>
+      <c r="I30" t="s">
+        <v>318</v>
+      </c>
+      <c r="J30" t="s">
+        <v>319</v>
+      </c>
+      <c r="K30" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B31" t="s">
+        <v>322</v>
+      </c>
+      <c r="C31" t="s">
+        <v>323</v>
+      </c>
+      <c r="D31" t="s">
+        <v>324</v>
+      </c>
+      <c r="E31" t="s">
+        <v>325</v>
+      </c>
+      <c r="F31" t="s">
+        <v>326</v>
+      </c>
+      <c r="G31" t="s">
+        <v>327</v>
+      </c>
+      <c r="H31" t="s">
+        <v>328</v>
+      </c>
+      <c r="I31" t="s">
+        <v>329</v>
+      </c>
+      <c r="J31" t="s">
+        <v>330</v>
+      </c>
+      <c r="K31" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>332</v>
+      </c>
+      <c r="B32" t="s">
+        <v>333</v>
+      </c>
+      <c r="C32" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" t="s">
+        <v>335</v>
+      </c>
+      <c r="E32" t="s">
+        <v>336</v>
+      </c>
+      <c r="F32" t="s">
+        <v>337</v>
+      </c>
+      <c r="G32" t="s">
+        <v>338</v>
+      </c>
+      <c r="H32" t="s">
+        <v>339</v>
+      </c>
+      <c r="I32" t="s">
+        <v>340</v>
+      </c>
+      <c r="J32" t="s">
+        <v>341</v>
+      </c>
+      <c r="K32" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>343</v>
+      </c>
+      <c r="B33" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" t="s">
+        <v>345</v>
+      </c>
+      <c r="D33" t="s">
+        <v>346</v>
+      </c>
+      <c r="E33" t="s">
+        <v>347</v>
+      </c>
+      <c r="F33" t="s">
+        <v>348</v>
+      </c>
+      <c r="G33" t="s">
+        <v>349</v>
+      </c>
+      <c r="H33" t="s">
+        <v>350</v>
+      </c>
+      <c r="I33" t="s">
+        <v>351</v>
+      </c>
+      <c r="J33" t="s">
+        <v>352</v>
+      </c>
+      <c r="K33" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>354</v>
+      </c>
+      <c r="B34" t="s">
+        <v>355</v>
+      </c>
+      <c r="C34" t="s">
+        <v>356</v>
+      </c>
+      <c r="D34" t="s">
+        <v>357</v>
+      </c>
+      <c r="E34" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" t="s">
+        <v>358</v>
+      </c>
+      <c r="G34" t="s">
+        <v>359</v>
+      </c>
+      <c r="H34" t="s">
+        <v>360</v>
+      </c>
+      <c r="I34" t="s">
+        <v>361</v>
+      </c>
+      <c r="J34" t="s">
+        <v>362</v>
+      </c>
+      <c r="K34" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>364</v>
+      </c>
+      <c r="B35" t="s">
+        <v>365</v>
+      </c>
+      <c r="C35" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" t="s">
+        <v>367</v>
+      </c>
+      <c r="E35" t="s">
+        <v>325</v>
+      </c>
+      <c r="F35" t="s">
+        <v>368</v>
+      </c>
+      <c r="G35" t="s">
+        <v>369</v>
+      </c>
+      <c r="H35" t="s">
+        <v>370</v>
+      </c>
+      <c r="I35" t="s">
+        <v>371</v>
+      </c>
+      <c r="J35" t="s">
+        <v>372</v>
+      </c>
+      <c r="K35" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>374</v>
+      </c>
+      <c r="B36" t="s">
+        <v>375</v>
+      </c>
+      <c r="C36" t="s">
+        <v>376</v>
+      </c>
+      <c r="D36" t="s">
+        <v>377</v>
+      </c>
+      <c r="E36" t="s">
+        <v>378</v>
+      </c>
+      <c r="F36" t="s">
+        <v>379</v>
+      </c>
+      <c r="G36" t="s">
+        <v>380</v>
+      </c>
+      <c r="H36" t="s">
+        <v>381</v>
+      </c>
+      <c r="I36" t="s">
+        <v>382</v>
+      </c>
+      <c r="J36" t="s">
+        <v>383</v>
+      </c>
+      <c r="K36" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>385</v>
+      </c>
+      <c r="B37" t="s">
+        <v>386</v>
+      </c>
+      <c r="C37" t="s">
+        <v>387</v>
+      </c>
+      <c r="D37" t="s">
+        <v>388</v>
+      </c>
+      <c r="E37" t="s">
+        <v>389</v>
+      </c>
+      <c r="F37" t="s">
+        <v>390</v>
+      </c>
+      <c r="G37" t="s">
+        <v>391</v>
+      </c>
+      <c r="H37" t="s">
+        <v>392</v>
+      </c>
+      <c r="I37" t="s">
+        <v>393</v>
+      </c>
+      <c r="J37" t="s">
+        <v>394</v>
+      </c>
+      <c r="K37" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>396</v>
+      </c>
+      <c r="B38" t="s">
+        <v>397</v>
+      </c>
+      <c r="C38" t="s">
+        <v>398</v>
+      </c>
+      <c r="D38" t="s">
+        <v>399</v>
+      </c>
+      <c r="E38" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>400</v>
+      </c>
+      <c r="G38" t="s">
+        <v>401</v>
+      </c>
+      <c r="H38" t="s">
+        <v>402</v>
+      </c>
+      <c r="I38" t="s">
+        <v>403</v>
+      </c>
+      <c r="J38" t="s">
+        <v>404</v>
+      </c>
+      <c r="K38" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>406</v>
+      </c>
+      <c r="B39" t="s">
+        <v>407</v>
+      </c>
+      <c r="C39" t="s">
+        <v>408</v>
+      </c>
+      <c r="D39" t="s">
+        <v>409</v>
+      </c>
+      <c r="E39" t="s">
+        <v>282</v>
+      </c>
+      <c r="F39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G39" t="s">
+        <v>411</v>
+      </c>
+      <c r="H39" t="s">
+        <v>412</v>
+      </c>
+      <c r="I39" t="s">
+        <v>413</v>
+      </c>
+      <c r="J39" t="s">
+        <v>414</v>
+      </c>
+      <c r="K39" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>416</v>
+      </c>
+      <c r="B40" t="s">
+        <v>417</v>
+      </c>
+      <c r="C40" t="s">
+        <v>418</v>
+      </c>
+      <c r="D40" t="s">
+        <v>419</v>
+      </c>
+      <c r="E40" t="s">
+        <v>420</v>
+      </c>
+      <c r="F40" t="s">
+        <v>421</v>
+      </c>
+      <c r="G40" t="s">
+        <v>422</v>
+      </c>
+      <c r="H40" t="s">
+        <v>423</v>
+      </c>
+      <c r="I40" t="s">
+        <v>424</v>
+      </c>
+      <c r="J40" t="s">
+        <v>425</v>
+      </c>
+      <c r="K40" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>427</v>
+      </c>
+      <c r="B41" t="s">
+        <v>428</v>
+      </c>
+      <c r="C41" t="s">
+        <v>429</v>
+      </c>
+      <c r="D41" t="s">
+        <v>430</v>
+      </c>
+      <c r="E41" t="s">
+        <v>431</v>
+      </c>
+      <c r="F41" t="s">
+        <v>432</v>
+      </c>
+      <c r="G41" t="s">
+        <v>433</v>
+      </c>
+      <c r="H41" t="s">
+        <v>434</v>
+      </c>
+      <c r="I41" t="s">
+        <v>435</v>
+      </c>
+      <c r="J41" t="s">
+        <v>436</v>
+      </c>
+      <c r="K41" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>438</v>
+      </c>
+      <c r="B42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C42" t="s">
+        <v>440</v>
+      </c>
+      <c r="D42" t="s">
+        <v>441</v>
+      </c>
+      <c r="E42" t="s">
+        <v>442</v>
+      </c>
+      <c r="F42" t="s">
+        <v>443</v>
+      </c>
+      <c r="G42" t="s">
+        <v>444</v>
+      </c>
+      <c r="H42" t="s">
+        <v>445</v>
+      </c>
+      <c r="I42" t="s">
+        <v>446</v>
+      </c>
+      <c r="J42" t="s">
+        <v>447</v>
+      </c>
+      <c r="K42" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>449</v>
+      </c>
+      <c r="B43" t="s">
+        <v>450</v>
+      </c>
+      <c r="C43" t="s">
+        <v>451</v>
+      </c>
+      <c r="D43" t="s">
+        <v>452</v>
+      </c>
+      <c r="E43" t="s">
+        <v>453</v>
+      </c>
+      <c r="F43" t="s">
+        <v>454</v>
+      </c>
+      <c r="G43" t="s">
+        <v>455</v>
+      </c>
+      <c r="H43" t="s">
+        <v>456</v>
+      </c>
+      <c r="I43" t="s">
+        <v>457</v>
+      </c>
+      <c r="J43" t="s">
+        <v>458</v>
+      </c>
+      <c r="K43" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>460</v>
+      </c>
+      <c r="B44" t="s">
+        <v>461</v>
+      </c>
+      <c r="C44" t="s">
+        <v>462</v>
+      </c>
+      <c r="D44" t="s">
+        <v>463</v>
+      </c>
+      <c r="E44" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" t="s">
+        <v>464</v>
+      </c>
+      <c r="G44" t="s">
+        <v>465</v>
+      </c>
+      <c r="H44" t="s">
+        <v>466</v>
+      </c>
+      <c r="I44" t="s">
+        <v>467</v>
+      </c>
+      <c r="J44" t="s">
+        <v>468</v>
+      </c>
+      <c r="K44" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>470</v>
+      </c>
+      <c r="B45" t="s">
+        <v>471</v>
+      </c>
+      <c r="C45" t="s">
+        <v>472</v>
+      </c>
+      <c r="D45" t="s">
+        <v>473</v>
+      </c>
+      <c r="E45" t="s">
+        <v>474</v>
+      </c>
+      <c r="F45" t="s">
+        <v>475</v>
+      </c>
+      <c r="G45" t="s">
+        <v>476</v>
+      </c>
+      <c r="H45" t="s">
+        <v>477</v>
+      </c>
+      <c r="I45" t="s">
+        <v>478</v>
+      </c>
+      <c r="J45" t="s">
+        <v>479</v>
+      </c>
+      <c r="K45" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>481</v>
+      </c>
+      <c r="B46" t="s">
+        <v>482</v>
+      </c>
+      <c r="C46" t="s">
+        <v>483</v>
+      </c>
+      <c r="D46" t="s">
+        <v>484</v>
+      </c>
+      <c r="E46" t="s">
+        <v>485</v>
+      </c>
+      <c r="F46" t="s">
+        <v>486</v>
+      </c>
+      <c r="G46" t="s">
+        <v>487</v>
+      </c>
+      <c r="H46" t="s">
+        <v>488</v>
+      </c>
+      <c r="I46" t="s">
+        <v>489</v>
+      </c>
+      <c r="J46" t="s">
+        <v>490</v>
+      </c>
+      <c r="K46" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>492</v>
+      </c>
+      <c r="B47" t="s">
+        <v>493</v>
+      </c>
+      <c r="C47" t="s">
+        <v>494</v>
+      </c>
+      <c r="D47" t="s">
+        <v>495</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
+        <v>496</v>
+      </c>
+      <c r="G47" t="s">
+        <v>497</v>
+      </c>
+      <c r="H47" t="s">
+        <v>498</v>
+      </c>
+      <c r="I47" t="s">
+        <v>499</v>
+      </c>
+      <c r="J47" t="s">
+        <v>500</v>
+      </c>
+      <c r="K47" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>502</v>
+      </c>
+      <c r="B48" t="s">
+        <v>503</v>
+      </c>
+      <c r="C48" t="s">
+        <v>504</v>
+      </c>
+      <c r="D48" t="s">
+        <v>505</v>
+      </c>
+      <c r="E48" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" t="s">
+        <v>506</v>
+      </c>
+      <c r="G48" t="s">
+        <v>507</v>
+      </c>
+      <c r="H48" t="s">
+        <v>508</v>
+      </c>
+      <c r="I48" t="s">
+        <v>509</v>
+      </c>
+      <c r="J48" t="s">
+        <v>510</v>
+      </c>
+      <c r="K48" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>512</v>
+      </c>
+      <c r="B49" t="s">
+        <v>513</v>
+      </c>
+      <c r="C49" t="s">
+        <v>514</v>
+      </c>
+      <c r="D49" t="s">
+        <v>515</v>
+      </c>
+      <c r="E49" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" t="s">
+        <v>516</v>
+      </c>
+      <c r="G49" t="s">
+        <v>517</v>
+      </c>
+      <c r="H49" t="s">
+        <v>518</v>
+      </c>
+      <c r="I49" t="s">
+        <v>519</v>
+      </c>
+      <c r="J49" t="s">
+        <v>520</v>
+      </c>
+      <c r="K49" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>522</v>
+      </c>
+      <c r="B50" t="s">
+        <v>523</v>
+      </c>
+      <c r="C50" t="s">
+        <v>524</v>
+      </c>
+      <c r="D50" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" t="s">
+        <v>37</v>
+      </c>
+      <c r="F50" t="s">
+        <v>525</v>
+      </c>
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" t="s">
+        <v>526</v>
+      </c>
+      <c r="I50" t="s">
+        <v>527</v>
+      </c>
+      <c r="J50" t="s">
+        <v>528</v>
+      </c>
+      <c r="K50" t="s">
+        <v>529</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>